--- a/output/yearly_population_iteration_35_growth_param_0.5.xlsx
+++ b/output/yearly_population_iteration_35_growth_param_0.5.xlsx
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4145</v>
+        <v>4312</v>
       </c>
       <c r="C2" t="n">
-        <v>8522</v>
+        <v>8506</v>
       </c>
       <c r="D2" t="n">
-        <v>21978</v>
+        <v>27548</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2689</v>
+        <v>3089</v>
       </c>
       <c r="C3" t="n">
-        <v>7796</v>
+        <v>7475</v>
       </c>
       <c r="D3" t="n">
-        <v>16145</v>
+        <v>15656</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2137</v>
+        <v>2435</v>
       </c>
       <c r="C4" t="n">
-        <v>6696</v>
+        <v>7151</v>
       </c>
       <c r="D4" t="n">
-        <v>8053</v>
+        <v>7176</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1528</v>
+        <v>1514</v>
       </c>
       <c r="C5" t="n">
-        <v>5885</v>
+        <v>5411</v>
       </c>
       <c r="D5" t="n">
-        <v>3057</v>
+        <v>2708</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>920</v>
+        <v>826</v>
       </c>
       <c r="C6" t="n">
-        <v>4059</v>
+        <v>3950</v>
       </c>
       <c r="D6" t="n">
-        <v>1221</v>
+        <v>1106</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>438</v>
+        <v>385</v>
       </c>
       <c r="C7" t="n">
-        <v>2469</v>
+        <v>2743</v>
       </c>
       <c r="D7" t="n">
-        <v>661</v>
+        <v>639</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>164</v>
+        <v>142</v>
       </c>
       <c r="C8" t="n">
-        <v>1126</v>
+        <v>1387</v>
       </c>
       <c r="D8" t="n">
-        <v>422</v>
+        <v>419</v>
       </c>
     </row>
     <row r="9">
@@ -878,10 +878,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="C9" t="n">
-        <v>453</v>
+        <v>532</v>
       </c>
       <c r="D9" t="n">
         <v>304</v>
@@ -895,7 +895,7 @@
         <v>37</v>
       </c>
       <c r="C10" t="n">
-        <v>220</v>
+        <v>229</v>
       </c>
       <c r="D10" t="n">
         <v>243</v>
@@ -909,10 +909,10 @@
         <v>26</v>
       </c>
       <c r="C11" t="n">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="D11" t="n">
-        <v>202</v>
+        <v>204</v>
       </c>
     </row>
     <row r="12">
@@ -923,10 +923,10 @@
         <v>16</v>
       </c>
       <c r="C12" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D12" t="n">
-        <v>159</v>
+        <v>157</v>
       </c>
     </row>
     <row r="13">
@@ -940,7 +940,7 @@
         <v>96</v>
       </c>
       <c r="D13" t="n">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="14">
@@ -951,7 +951,7 @@
         <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D14" t="n">
         <v>98</v>
@@ -965,7 +965,7 @@
         <v>3</v>
       </c>
       <c r="C15" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D15" t="n">
         <v>82</v>
@@ -982,7 +982,7 @@
         <v>44</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="17">
@@ -1021,7 +1021,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D19" t="n">
         <v>26</v>
@@ -1035,7 +1035,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D20" t="n">
         <v>16</v>
@@ -1049,7 +1049,7 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D21" t="n">
         <v>8</v>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6410</v>
+        <v>4721</v>
       </c>
       <c r="C2" t="n">
-        <v>7970</v>
+        <v>11114</v>
       </c>
       <c r="D2" t="n">
-        <v>32465</v>
+        <v>25905</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2690</v>
+        <v>2950</v>
       </c>
       <c r="C3" t="n">
-        <v>7170</v>
+        <v>7001</v>
       </c>
       <c r="D3" t="n">
-        <v>15832</v>
+        <v>16151</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2022</v>
+        <v>2312</v>
       </c>
       <c r="C4" t="n">
-        <v>6988</v>
+        <v>7148</v>
       </c>
       <c r="D4" t="n">
-        <v>9051</v>
+        <v>8260</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1581</v>
+        <v>1683</v>
       </c>
       <c r="C5" t="n">
-        <v>6120</v>
+        <v>5998</v>
       </c>
       <c r="D5" t="n">
-        <v>3654</v>
+        <v>3243</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1074</v>
+        <v>999</v>
       </c>
       <c r="C6" t="n">
-        <v>4753</v>
+        <v>4492</v>
       </c>
       <c r="D6" t="n">
-        <v>1457</v>
+        <v>1322</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>564</v>
+        <v>501</v>
       </c>
       <c r="C7" t="n">
-        <v>3138</v>
+        <v>3250</v>
       </c>
       <c r="D7" t="n">
-        <v>736</v>
+        <v>690</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>239</v>
+        <v>208</v>
       </c>
       <c r="C8" t="n">
-        <v>1654</v>
+        <v>1917</v>
       </c>
       <c r="D8" t="n">
-        <v>446</v>
+        <v>444</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="C9" t="n">
-        <v>712</v>
+        <v>866</v>
       </c>
       <c r="D9" t="n">
-        <v>317</v>
+        <v>312</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C10" t="n">
-        <v>308</v>
+        <v>339</v>
       </c>
       <c r="D10" t="n">
-        <v>245</v>
+        <v>248</v>
       </c>
     </row>
     <row r="11">
@@ -1220,10 +1220,10 @@
         <v>27</v>
       </c>
       <c r="C11" t="n">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="D11" t="n">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="12">
@@ -1234,10 +1234,10 @@
         <v>17</v>
       </c>
       <c r="C12" t="n">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="D12" t="n">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="13">
@@ -1251,7 +1251,7 @@
         <v>104</v>
       </c>
       <c r="D13" t="n">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="14">
@@ -1276,7 +1276,7 @@
         <v>3</v>
       </c>
       <c r="C15" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D15" t="n">
         <v>82</v>
@@ -1293,7 +1293,7 @@
         <v>47</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="17">
@@ -1332,7 +1332,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D19" t="n">
         <v>26</v>
@@ -1346,7 +1346,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D20" t="n">
         <v>16</v>
@@ -1360,7 +1360,7 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D21" t="n">
         <v>9</v>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7235</v>
+        <v>5780</v>
       </c>
       <c r="C2" t="n">
-        <v>10374</v>
+        <v>13108</v>
       </c>
       <c r="D2" t="n">
-        <v>26813</v>
+        <v>25856</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3284</v>
+        <v>2955</v>
       </c>
       <c r="C3" t="n">
-        <v>6670</v>
+        <v>7632</v>
       </c>
       <c r="D3" t="n">
-        <v>16706</v>
+        <v>16235</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1939</v>
+        <v>2179</v>
       </c>
       <c r="C4" t="n">
-        <v>6848</v>
+        <v>6871</v>
       </c>
       <c r="D4" t="n">
-        <v>9600</v>
+        <v>8990</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1564</v>
+        <v>1711</v>
       </c>
       <c r="C5" t="n">
-        <v>6275</v>
+        <v>6268</v>
       </c>
       <c r="D5" t="n">
-        <v>4233</v>
+        <v>3787</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1156</v>
+        <v>1140</v>
       </c>
       <c r="C6" t="n">
-        <v>5191</v>
+        <v>5032</v>
       </c>
       <c r="D6" t="n">
-        <v>1733</v>
+        <v>1562</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>677</v>
+        <v>614</v>
       </c>
       <c r="C7" t="n">
-        <v>3753</v>
+        <v>3679</v>
       </c>
       <c r="D7" t="n">
-        <v>813</v>
+        <v>756</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>316</v>
+        <v>278</v>
       </c>
       <c r="C8" t="n">
-        <v>2175</v>
+        <v>2380</v>
       </c>
       <c r="D8" t="n">
-        <v>478</v>
+        <v>470</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>124</v>
+        <v>110</v>
       </c>
       <c r="C9" t="n">
-        <v>1037</v>
+        <v>1227</v>
       </c>
       <c r="D9" t="n">
-        <v>325</v>
+        <v>321</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="C10" t="n">
-        <v>446</v>
+        <v>519</v>
       </c>
       <c r="D10" t="n">
-        <v>250</v>
+        <v>252</v>
       </c>
     </row>
     <row r="11">
@@ -1531,10 +1531,10 @@
         <v>28</v>
       </c>
       <c r="C11" t="n">
-        <v>220</v>
+        <v>232</v>
       </c>
       <c r="D11" t="n">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="12">
@@ -1545,10 +1545,10 @@
         <v>18</v>
       </c>
       <c r="C12" t="n">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="D12" t="n">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="13">
@@ -1559,10 +1559,10 @@
         <v>10</v>
       </c>
       <c r="C13" t="n">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D13" t="n">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="14">
@@ -1576,7 +1576,7 @@
         <v>87</v>
       </c>
       <c r="D14" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="15">
@@ -1587,10 +1587,10 @@
         <v>3</v>
       </c>
       <c r="C15" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D15" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="16">
@@ -1604,7 +1604,7 @@
         <v>50</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="17">
@@ -1643,7 +1643,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D19" t="n">
         <v>26</v>
@@ -1657,7 +1657,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D20" t="n">
         <v>16</v>
@@ -1671,7 +1671,7 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D21" t="n">
         <v>10</v>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6577</v>
+        <v>5333</v>
       </c>
       <c r="C2" t="n">
-        <v>7303</v>
+        <v>9228</v>
       </c>
       <c r="D2" t="n">
-        <v>22252</v>
+        <v>21619</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3666</v>
+        <v>3669</v>
       </c>
       <c r="C3" t="n">
-        <v>10357</v>
+        <v>11619</v>
       </c>
       <c r="D3" t="n">
-        <v>18277</v>
+        <v>17498</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1445</v>
+        <v>1580</v>
       </c>
       <c r="C4" t="n">
-        <v>9639</v>
+        <v>9579</v>
       </c>
       <c r="D4" t="n">
-        <v>9141</v>
+        <v>8436</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1068</v>
+        <v>1053</v>
       </c>
       <c r="C5" t="n">
-        <v>5087</v>
+        <v>4931</v>
       </c>
       <c r="D5" t="n">
-        <v>2795</v>
+        <v>2512</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>625</v>
+        <v>567</v>
       </c>
       <c r="C6" t="n">
-        <v>3677</v>
+        <v>3605</v>
       </c>
       <c r="D6" t="n">
-        <v>796</v>
+        <v>740</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>291</v>
+        <v>256</v>
       </c>
       <c r="C7" t="n">
-        <v>2131</v>
+        <v>2332</v>
       </c>
       <c r="D7" t="n">
-        <v>468</v>
+        <v>460</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>114</v>
+        <v>101</v>
       </c>
       <c r="C8" t="n">
-        <v>1016</v>
+        <v>1202</v>
       </c>
       <c r="D8" t="n">
-        <v>318</v>
+        <v>314</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="C9" t="n">
-        <v>437</v>
+        <v>508</v>
       </c>
       <c r="D9" t="n">
-        <v>245</v>
+        <v>246</v>
       </c>
     </row>
     <row r="10">
@@ -1828,10 +1828,10 @@
         <v>25</v>
       </c>
       <c r="C10" t="n">
-        <v>215</v>
+        <v>227</v>
       </c>
       <c r="D10" t="n">
-        <v>200</v>
+        <v>199</v>
       </c>
     </row>
     <row r="11">
@@ -1842,10 +1842,10 @@
         <v>16</v>
       </c>
       <c r="C11" t="n">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D11" t="n">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="12">
@@ -1856,10 +1856,10 @@
         <v>9</v>
       </c>
       <c r="C12" t="n">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="D12" t="n">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="13">
@@ -1873,7 +1873,7 @@
         <v>85</v>
       </c>
       <c r="D13" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="14">
@@ -1884,10 +1884,10 @@
         <v>2</v>
       </c>
       <c r="C14" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D14" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="15">
@@ -1901,7 +1901,7 @@
         <v>49</v>
       </c>
       <c r="D15" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="16">
@@ -1940,7 +1940,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D18" t="n">
         <v>25</v>
@@ -1954,7 +1954,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D19" t="n">
         <v>15</v>
@@ -1968,7 +1968,7 @@
         <v>8</v>
       </c>
       <c r="C20" t="n">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D20" t="n">
         <v>10</v>
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3982</v>
+        <v>3329</v>
       </c>
       <c r="C2" t="n">
-        <v>3549</v>
+        <v>4364</v>
       </c>
       <c r="D2" t="n">
-        <v>15576</v>
+        <v>14938</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4123</v>
+        <v>3746</v>
       </c>
       <c r="C3" t="n">
-        <v>8231</v>
+        <v>9640</v>
       </c>
       <c r="D3" t="n">
-        <v>17762</v>
+        <v>17045</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1947</v>
+        <v>2036</v>
       </c>
       <c r="C4" t="n">
-        <v>10033</v>
+        <v>10648</v>
       </c>
       <c r="D4" t="n">
-        <v>10354</v>
+        <v>9646</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1151</v>
+        <v>1175</v>
       </c>
       <c r="C5" t="n">
-        <v>7017</v>
+        <v>6802</v>
       </c>
       <c r="D5" t="n">
-        <v>3494</v>
+        <v>3166</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>730</v>
+        <v>661</v>
       </c>
       <c r="C6" t="n">
-        <v>4362</v>
+        <v>4259</v>
       </c>
       <c r="D6" t="n">
-        <v>982</v>
+        <v>905</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>270</v>
+        <v>238</v>
       </c>
       <c r="C7" t="n">
-        <v>2675</v>
+        <v>2825</v>
       </c>
       <c r="D7" t="n">
-        <v>513</v>
+        <v>502</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>96</v>
+        <v>86</v>
       </c>
       <c r="C8" t="n">
-        <v>1337</v>
+        <v>1558</v>
       </c>
       <c r="D8" t="n">
-        <v>324</v>
+        <v>323</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C9" t="n">
-        <v>462</v>
+        <v>526</v>
       </c>
       <c r="D9" t="n">
-        <v>256</v>
+        <v>254</v>
       </c>
     </row>
     <row r="10">
@@ -2139,10 +2139,10 @@
         <v>14</v>
       </c>
       <c r="C10" t="n">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="D10" t="n">
-        <v>207</v>
+        <v>205</v>
       </c>
     </row>
     <row r="11">
@@ -2153,10 +2153,10 @@
         <v>8</v>
       </c>
       <c r="C11" t="n">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="D11" t="n">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="12">
@@ -2181,10 +2181,10 @@
         <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D13" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="14">
@@ -2198,7 +2198,7 @@
         <v>48</v>
       </c>
       <c r="D14" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="15">
@@ -2237,7 +2237,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D17" t="n">
         <v>24</v>
@@ -2251,7 +2251,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D18" t="n">
         <v>14</v>
@@ -2265,7 +2265,7 @@
         <v>7</v>
       </c>
       <c r="C19" t="n">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D19" t="n">
         <v>9</v>
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3582</v>
+        <v>3892</v>
       </c>
       <c r="C2" t="n">
-        <v>5947</v>
+        <v>8105</v>
       </c>
       <c r="D2" t="n">
-        <v>15372</v>
+        <v>16335</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3448</v>
+        <v>3038</v>
       </c>
       <c r="C3" t="n">
-        <v>5421</v>
+        <v>6430</v>
       </c>
       <c r="D3" t="n">
-        <v>16441</v>
+        <v>15776</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2415</v>
+        <v>2337</v>
       </c>
       <c r="C4" t="n">
-        <v>8976</v>
+        <v>10054</v>
       </c>
       <c r="D4" t="n">
-        <v>11077</v>
+        <v>10396</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1315</v>
+        <v>1358</v>
       </c>
       <c r="C5" t="n">
-        <v>8299</v>
+        <v>8358</v>
       </c>
       <c r="D5" t="n">
-        <v>4441</v>
+        <v>4065</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>827</v>
+        <v>790</v>
       </c>
       <c r="C6" t="n">
-        <v>5443</v>
+        <v>5293</v>
       </c>
       <c r="D6" t="n">
-        <v>1330</v>
+        <v>1218</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>391</v>
+        <v>349</v>
       </c>
       <c r="C7" t="n">
-        <v>3394</v>
+        <v>3441</v>
       </c>
       <c r="D7" t="n">
-        <v>572</v>
+        <v>557</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>135</v>
+        <v>120</v>
       </c>
       <c r="C8" t="n">
-        <v>1860</v>
+        <v>2056</v>
       </c>
       <c r="D8" t="n">
-        <v>347</v>
+        <v>340</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="C9" t="n">
-        <v>775</v>
+        <v>895</v>
       </c>
       <c r="D9" t="n">
-        <v>260</v>
+        <v>258</v>
       </c>
     </row>
     <row r="10">
@@ -2450,10 +2450,10 @@
         <v>17</v>
       </c>
       <c r="C10" t="n">
-        <v>308</v>
+        <v>335</v>
       </c>
       <c r="D10" t="n">
-        <v>211</v>
+        <v>209</v>
       </c>
     </row>
     <row r="11">
@@ -2464,10 +2464,10 @@
         <v>8</v>
       </c>
       <c r="C11" t="n">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="D11" t="n">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="12">
@@ -2492,10 +2492,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D13" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="14">
@@ -2506,10 +2506,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D14" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="15">
@@ -2520,7 +2520,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D15" t="n">
         <v>47</v>
@@ -2548,7 +2548,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D17" t="n">
         <v>22</v>
@@ -2562,7 +2562,7 @@
         <v>6</v>
       </c>
       <c r="C18" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D18" t="n">
         <v>13</v>
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2156</v>
+        <v>2328</v>
       </c>
       <c r="C2" t="n">
-        <v>2863</v>
+        <v>4011</v>
       </c>
       <c r="D2" t="n">
-        <v>10748</v>
+        <v>11537</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3358</v>
+        <v>3144</v>
       </c>
       <c r="C3" t="n">
-        <v>5441</v>
+        <v>6787</v>
       </c>
       <c r="D3" t="n">
-        <v>15961</v>
+        <v>15501</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2677</v>
+        <v>2551</v>
       </c>
       <c r="C4" t="n">
-        <v>8558</v>
+        <v>9731</v>
       </c>
       <c r="D4" t="n">
-        <v>11820</v>
+        <v>11070</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1390</v>
+        <v>1402</v>
       </c>
       <c r="C5" t="n">
-        <v>9878</v>
+        <v>10031</v>
       </c>
       <c r="D5" t="n">
-        <v>4653</v>
+        <v>4167</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>682</v>
+        <v>629</v>
       </c>
       <c r="C6" t="n">
-        <v>6277</v>
+        <v>6193</v>
       </c>
       <c r="D6" t="n">
-        <v>1287</v>
+        <v>1186</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>124</v>
+        <v>110</v>
       </c>
       <c r="C7" t="n">
-        <v>3489</v>
+        <v>3622</v>
       </c>
       <c r="D7" t="n">
-        <v>570</v>
+        <v>556</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="C8" t="n">
-        <v>1288</v>
+        <v>1461</v>
       </c>
       <c r="D8" t="n">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="9">
@@ -2747,10 +2747,10 @@
         <v>15</v>
       </c>
       <c r="C9" t="n">
-        <v>301</v>
+        <v>328</v>
       </c>
       <c r="D9" t="n">
-        <v>283</v>
+        <v>278</v>
       </c>
     </row>
     <row r="10">
@@ -2761,10 +2761,10 @@
         <v>7</v>
       </c>
       <c r="C10" t="n">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="D10" t="n">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="11">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D12" t="n">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="13">
@@ -2803,10 +2803,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D13" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="14">
@@ -2817,7 +2817,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D14" t="n">
         <v>46</v>
@@ -2845,7 +2845,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D16" t="n">
         <v>21</v>
@@ -2859,7 +2859,7 @@
         <v>5</v>
       </c>
       <c r="C17" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D17" t="n">
         <v>12</v>
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2322</v>
+        <v>2533</v>
       </c>
       <c r="C2" t="n">
-        <v>7419</v>
+        <v>7947</v>
       </c>
       <c r="D2" t="n">
-        <v>11299</v>
+        <v>12552</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2475</v>
+        <v>2413</v>
       </c>
       <c r="C3" t="n">
-        <v>3867</v>
+        <v>4993</v>
       </c>
       <c r="D3" t="n">
-        <v>14246</v>
+        <v>13976</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2563</v>
+        <v>2425</v>
       </c>
       <c r="C4" t="n">
-        <v>6973</v>
+        <v>8293</v>
       </c>
       <c r="D4" t="n">
-        <v>12096</v>
+        <v>11414</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1674</v>
+        <v>1645</v>
       </c>
       <c r="C5" t="n">
-        <v>9197</v>
+        <v>9791</v>
       </c>
       <c r="D5" t="n">
-        <v>5543</v>
+        <v>5074</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>857</v>
+        <v>824</v>
       </c>
       <c r="C6" t="n">
-        <v>7735</v>
+        <v>7711</v>
       </c>
       <c r="D6" t="n">
-        <v>1735</v>
+        <v>1542</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>249</v>
+        <v>226</v>
       </c>
       <c r="C7" t="n">
-        <v>4621</v>
+        <v>4613</v>
       </c>
       <c r="D7" t="n">
-        <v>648</v>
+        <v>624</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="C8" t="n">
-        <v>2067</v>
+        <v>2230</v>
       </c>
       <c r="D8" t="n">
-        <v>389</v>
+        <v>386</v>
       </c>
     </row>
     <row r="9">
@@ -3058,10 +3058,10 @@
         <v>18</v>
       </c>
       <c r="C9" t="n">
-        <v>609</v>
+        <v>681</v>
       </c>
       <c r="D9" t="n">
-        <v>290</v>
+        <v>288</v>
       </c>
     </row>
     <row r="10">
@@ -3072,10 +3072,10 @@
         <v>7</v>
       </c>
       <c r="C10" t="n">
-        <v>215</v>
+        <v>225</v>
       </c>
       <c r="D10" t="n">
-        <v>173</v>
+        <v>169</v>
       </c>
     </row>
     <row r="11">
@@ -3086,7 +3086,7 @@
         <v>2</v>
       </c>
       <c r="C11" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D11" t="n">
         <v>133</v>
@@ -3103,7 +3103,7 @@
         <v>77</v>
       </c>
       <c r="D12" t="n">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="13">
@@ -3117,7 +3117,7 @@
         <v>56</v>
       </c>
       <c r="D13" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="14">
@@ -3128,7 +3128,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D14" t="n">
         <v>45</v>
@@ -3142,7 +3142,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D15" t="n">
         <v>32</v>
@@ -3156,7 +3156,7 @@
         <v>4</v>
       </c>
       <c r="C16" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D16" t="n">
         <v>19</v>
@@ -3170,7 +3170,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D17" t="n">
         <v>9</v>
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1565</v>
+        <v>1697</v>
       </c>
       <c r="C2" t="n">
-        <v>5036</v>
+        <v>4848</v>
       </c>
       <c r="D2" t="n">
-        <v>8498</v>
+        <v>9462</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2131</v>
+        <v>2148</v>
       </c>
       <c r="C3" t="n">
-        <v>4779</v>
+        <v>5546</v>
       </c>
       <c r="D3" t="n">
-        <v>13163</v>
+        <v>13078</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2315</v>
+        <v>2228</v>
       </c>
       <c r="C4" t="n">
-        <v>5836</v>
+        <v>7092</v>
       </c>
       <c r="D4" t="n">
-        <v>12112</v>
+        <v>11496</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1835</v>
+        <v>1766</v>
       </c>
       <c r="C5" t="n">
-        <v>8523</v>
+        <v>9459</v>
       </c>
       <c r="D5" t="n">
-        <v>6172</v>
+        <v>5686</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>985</v>
+        <v>949</v>
       </c>
       <c r="C6" t="n">
-        <v>8485</v>
+        <v>8620</v>
       </c>
       <c r="D6" t="n">
-        <v>2040</v>
+        <v>1825</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>222</v>
+        <v>202</v>
       </c>
       <c r="C7" t="n">
-        <v>5638</v>
+        <v>5550</v>
       </c>
       <c r="D7" t="n">
-        <v>725</v>
+        <v>698</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="C8" t="n">
-        <v>2634</v>
+        <v>2821</v>
       </c>
       <c r="D8" t="n">
-        <v>404</v>
+        <v>395</v>
       </c>
     </row>
     <row r="9">
@@ -3369,10 +3369,10 @@
         <v>13</v>
       </c>
       <c r="C9" t="n">
-        <v>672</v>
+        <v>717</v>
       </c>
       <c r="D9" t="n">
-        <v>286</v>
+        <v>285</v>
       </c>
     </row>
     <row r="10">
@@ -3383,10 +3383,10 @@
         <v>2</v>
       </c>
       <c r="C10" t="n">
-        <v>216</v>
+        <v>223</v>
       </c>
       <c r="D10" t="n">
-        <v>178</v>
+        <v>173</v>
       </c>
     </row>
     <row r="11">
@@ -3425,10 +3425,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D13" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="14">
@@ -3439,7 +3439,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D14" t="n">
         <v>35</v>
@@ -3453,7 +3453,7 @@
         <v>3</v>
       </c>
       <c r="C15" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D15" t="n">
         <v>18</v>
@@ -3467,7 +3467,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D16" t="n">
         <v>8</v>
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2545</v>
+        <v>2034</v>
       </c>
       <c r="C2" t="n">
-        <v>13454</v>
+        <v>5147</v>
       </c>
       <c r="D2" t="n">
-        <v>12250</v>
+        <v>11291</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1636</v>
+        <v>1683</v>
       </c>
       <c r="C3" t="n">
-        <v>4353</v>
+        <v>4770</v>
       </c>
       <c r="D3" t="n">
-        <v>11819</v>
+        <v>11856</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1958</v>
+        <v>1932</v>
       </c>
       <c r="C4" t="n">
-        <v>5288</v>
+        <v>6267</v>
       </c>
       <c r="D4" t="n">
-        <v>11885</v>
+        <v>11359</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1834</v>
+        <v>1747</v>
       </c>
       <c r="C5" t="n">
-        <v>7313</v>
+        <v>8353</v>
       </c>
       <c r="D5" t="n">
-        <v>6666</v>
+        <v>6183</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1156</v>
+        <v>1122</v>
       </c>
       <c r="C6" t="n">
-        <v>8430</v>
+        <v>8857</v>
       </c>
       <c r="D6" t="n">
-        <v>2529</v>
+        <v>2283</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>401</v>
+        <v>371</v>
       </c>
       <c r="C7" t="n">
-        <v>6640</v>
+        <v>6685</v>
       </c>
       <c r="D7" t="n">
-        <v>872</v>
+        <v>823</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="C8" t="n">
-        <v>3659</v>
+        <v>3702</v>
       </c>
       <c r="D8" t="n">
-        <v>434</v>
+        <v>423</v>
       </c>
     </row>
     <row r="9">
@@ -3680,10 +3680,10 @@
         <v>18</v>
       </c>
       <c r="C9" t="n">
-        <v>1267</v>
+        <v>1362</v>
       </c>
       <c r="D9" t="n">
-        <v>294</v>
+        <v>292</v>
       </c>
     </row>
     <row r="10">
@@ -3694,10 +3694,10 @@
         <v>3</v>
       </c>
       <c r="C10" t="n">
-        <v>347</v>
+        <v>360</v>
       </c>
       <c r="D10" t="n">
-        <v>187</v>
+        <v>182</v>
       </c>
     </row>
     <row r="11">
@@ -3708,7 +3708,7 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D11" t="n">
         <v>135</v>
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D13" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="14">
@@ -3764,7 +3764,7 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D15" t="n">
         <v>17</v>
@@ -3778,7 +3778,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D16" t="n">
         <v>7</v>
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5463</v>
+        <v>4220</v>
       </c>
       <c r="C2" t="n">
-        <v>12045</v>
+        <v>15810</v>
       </c>
       <c r="D2" t="n">
-        <v>12968</v>
+        <v>6932</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1858</v>
+        <v>1485</v>
       </c>
       <c r="C2" t="n">
-        <v>7965</v>
+        <v>3047</v>
       </c>
       <c r="D2" t="n">
-        <v>9114</v>
+        <v>8401</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2227</v>
+        <v>2238</v>
       </c>
       <c r="C3" t="n">
-        <v>6693</v>
+        <v>5343</v>
       </c>
       <c r="D3" t="n">
-        <v>12945</v>
+        <v>12886</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2695</v>
+        <v>2585</v>
       </c>
       <c r="C4" t="n">
-        <v>7817</v>
+        <v>9129</v>
       </c>
       <c r="D4" t="n">
-        <v>12096</v>
+        <v>11516</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1085</v>
+        <v>1052</v>
       </c>
       <c r="C5" t="n">
-        <v>11337</v>
+        <v>12416</v>
       </c>
       <c r="D5" t="n">
-        <v>6063</v>
+        <v>5592</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>370</v>
+        <v>342</v>
       </c>
       <c r="C6" t="n">
-        <v>7994</v>
+        <v>8026</v>
       </c>
       <c r="D6" t="n">
-        <v>1966</v>
+        <v>1806</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="C7" t="n">
-        <v>3585</v>
+        <v>3627</v>
       </c>
       <c r="D7" t="n">
-        <v>527</v>
+        <v>511</v>
       </c>
     </row>
     <row r="8">
@@ -4288,10 +4288,10 @@
         <v>16</v>
       </c>
       <c r="C8" t="n">
-        <v>1241</v>
+        <v>1334</v>
       </c>
       <c r="D8" t="n">
-        <v>288</v>
+        <v>286</v>
       </c>
     </row>
     <row r="9">
@@ -4302,10 +4302,10 @@
         <v>2</v>
       </c>
       <c r="C9" t="n">
-        <v>340</v>
+        <v>352</v>
       </c>
       <c r="D9" t="n">
-        <v>183</v>
+        <v>178</v>
       </c>
     </row>
     <row r="10">
@@ -4316,7 +4316,7 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D10" t="n">
         <v>132</v>
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D12" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="13">
@@ -4372,7 +4372,7 @@
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D14" t="n">
         <v>16</v>
@@ -4386,7 +4386,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D15" t="n">
         <v>6</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6461</v>
+        <v>6115</v>
       </c>
       <c r="C2" t="n">
-        <v>7520</v>
+        <v>9522</v>
       </c>
       <c r="D2" t="n">
-        <v>20645</v>
+        <v>14844</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2321</v>
+        <v>1794</v>
       </c>
       <c r="C3" t="n">
-        <v>6070</v>
+        <v>7968</v>
       </c>
       <c r="D3" t="n">
-        <v>2817</v>
+        <v>1803</v>
       </c>
     </row>
     <row r="4">
@@ -4557,7 +4557,7 @@
         <v>193</v>
       </c>
       <c r="C5" t="n">
-        <v>385</v>
+        <v>381</v>
       </c>
       <c r="D5" t="n">
         <v>1161</v>
@@ -4571,7 +4571,7 @@
         <v>200</v>
       </c>
       <c r="C6" t="n">
-        <v>454</v>
+        <v>459</v>
       </c>
       <c r="D6" t="n">
         <v>816</v>
@@ -4596,7 +4596,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C8" t="n">
         <v>260</v>
@@ -4610,7 +4610,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C9" t="n">
         <v>205</v>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5512</v>
+        <v>4484</v>
       </c>
       <c r="C2" t="n">
-        <v>6862</v>
+        <v>5727</v>
       </c>
       <c r="D2" t="n">
-        <v>27021</v>
+        <v>24938</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3605</v>
+        <v>3243</v>
       </c>
       <c r="C3" t="n">
-        <v>5942</v>
+        <v>7629</v>
       </c>
       <c r="D3" t="n">
-        <v>5604</v>
+        <v>3861</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1042</v>
+        <v>813</v>
       </c>
       <c r="C4" t="n">
-        <v>3600</v>
+        <v>4712</v>
       </c>
       <c r="D4" t="n">
-        <v>1749</v>
+        <v>1544</v>
       </c>
     </row>
     <row r="5">
@@ -4868,7 +4868,7 @@
         <v>125</v>
       </c>
       <c r="C5" t="n">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="D5" t="n">
         <v>1198</v>
@@ -4882,7 +4882,7 @@
         <v>185</v>
       </c>
       <c r="C6" t="n">
-        <v>410</v>
+        <v>406</v>
       </c>
       <c r="D6" t="n">
         <v>859</v>
@@ -4896,7 +4896,7 @@
         <v>160</v>
       </c>
       <c r="C7" t="n">
-        <v>402</v>
+        <v>409</v>
       </c>
       <c r="D7" t="n">
         <v>584</v>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4428</v>
+        <v>4255</v>
       </c>
       <c r="C2" t="n">
-        <v>12879</v>
+        <v>6755</v>
       </c>
       <c r="D2" t="n">
-        <v>25883</v>
+        <v>25943</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3713</v>
+        <v>3158</v>
       </c>
       <c r="C3" t="n">
-        <v>5579</v>
+        <v>5733</v>
       </c>
       <c r="D3" t="n">
-        <v>8627</v>
+        <v>6955</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1944</v>
+        <v>1693</v>
       </c>
       <c r="C4" t="n">
-        <v>4829</v>
+        <v>6238</v>
       </c>
       <c r="D4" t="n">
-        <v>2435</v>
+        <v>1941</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>480</v>
+        <v>389</v>
       </c>
       <c r="C5" t="n">
-        <v>2032</v>
+        <v>2629</v>
       </c>
       <c r="D5" t="n">
-        <v>1262</v>
+        <v>1224</v>
       </c>
     </row>
     <row r="6">
@@ -5193,7 +5193,7 @@
         <v>147</v>
       </c>
       <c r="C6" t="n">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="D6" t="n">
         <v>897</v>
@@ -5207,7 +5207,7 @@
         <v>160</v>
       </c>
       <c r="C7" t="n">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="D7" t="n">
         <v>626</v>
@@ -5221,7 +5221,7 @@
         <v>124</v>
       </c>
       <c r="C8" t="n">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="D8" t="n">
         <v>454</v>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4184</v>
+        <v>4452</v>
       </c>
       <c r="C2" t="n">
-        <v>6297</v>
+        <v>9106</v>
       </c>
       <c r="D2" t="n">
-        <v>24540</v>
+        <v>31388</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3337</v>
+        <v>3018</v>
       </c>
       <c r="C3" t="n">
-        <v>8076</v>
+        <v>5448</v>
       </c>
       <c r="D3" t="n">
-        <v>10642</v>
+        <v>9351</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2382</v>
+        <v>2045</v>
       </c>
       <c r="C4" t="n">
-        <v>5124</v>
+        <v>5841</v>
       </c>
       <c r="D4" t="n">
-        <v>3490</v>
+        <v>2796</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>981</v>
+        <v>839</v>
       </c>
       <c r="C5" t="n">
-        <v>3393</v>
+        <v>4410</v>
       </c>
       <c r="D5" t="n">
-        <v>1426</v>
+        <v>1310</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>270</v>
+        <v>234</v>
       </c>
       <c r="C6" t="n">
-        <v>1164</v>
+        <v>1436</v>
       </c>
       <c r="D6" t="n">
-        <v>935</v>
+        <v>929</v>
       </c>
     </row>
     <row r="7">
@@ -5529,10 +5529,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C8" t="n">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="D8" t="n">
         <v>471</v>
@@ -5543,10 +5543,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C9" t="n">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="D9" t="n">
         <v>380</v>
@@ -5686,7 +5686,7 @@
         <v>9</v>
       </c>
       <c r="C19" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D19" t="n">
         <v>42</v>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4991</v>
+        <v>6545</v>
       </c>
       <c r="C2" t="n">
-        <v>13682</v>
+        <v>11461</v>
       </c>
       <c r="D2" t="n">
-        <v>34628</v>
+        <v>26743</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2723</v>
+        <v>2687</v>
       </c>
       <c r="C3" t="n">
-        <v>5909</v>
+        <v>5943</v>
       </c>
       <c r="D3" t="n">
-        <v>11195</v>
+        <v>11163</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1767</v>
+        <v>1563</v>
       </c>
       <c r="C4" t="n">
-        <v>5431</v>
+        <v>4557</v>
       </c>
       <c r="D4" t="n">
-        <v>3996</v>
+        <v>3326</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>856</v>
+        <v>734</v>
       </c>
       <c r="C5" t="n">
-        <v>3115</v>
+        <v>3742</v>
       </c>
       <c r="D5" t="n">
-        <v>1408</v>
+        <v>1236</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>290</v>
+        <v>248</v>
       </c>
       <c r="C6" t="n">
-        <v>1502</v>
+        <v>1926</v>
       </c>
       <c r="D6" t="n">
-        <v>764</v>
+        <v>746</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="C7" t="n">
-        <v>474</v>
+        <v>557</v>
       </c>
       <c r="D7" t="n">
-        <v>519</v>
+        <v>518</v>
       </c>
     </row>
     <row r="8">
@@ -5840,10 +5840,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C8" t="n">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="D8" t="n">
         <v>352</v>
@@ -5857,7 +5857,7 @@
         <v>44</v>
       </c>
       <c r="C9" t="n">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="D9" t="n">
         <v>272</v>
@@ -5868,10 +5868,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C10" t="n">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="D10" t="n">
         <v>235</v>
@@ -5885,7 +5885,7 @@
         <v>21</v>
       </c>
       <c r="C11" t="n">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D11" t="n">
         <v>195</v>
@@ -5899,7 +5899,7 @@
         <v>13</v>
       </c>
       <c r="C12" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D12" t="n">
         <v>147</v>
@@ -5913,7 +5913,7 @@
         <v>9</v>
       </c>
       <c r="C13" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D13" t="n">
         <v>116</v>
@@ -5997,7 +5997,7 @@
         <v>2</v>
       </c>
       <c r="C19" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D19" t="n">
         <v>26</v>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3932</v>
+        <v>4508</v>
       </c>
       <c r="C2" t="n">
-        <v>6063</v>
+        <v>10899</v>
       </c>
       <c r="D2" t="n">
-        <v>28649</v>
+        <v>27116</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3173</v>
+        <v>3792</v>
       </c>
       <c r="C3" t="n">
-        <v>8889</v>
+        <v>7818</v>
       </c>
       <c r="D3" t="n">
-        <v>14307</v>
+        <v>12958</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1950</v>
+        <v>1833</v>
       </c>
       <c r="C4" t="n">
-        <v>5545</v>
+        <v>5230</v>
       </c>
       <c r="D4" t="n">
-        <v>5325</v>
+        <v>4804</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1148</v>
+        <v>1018</v>
       </c>
       <c r="C5" t="n">
-        <v>4384</v>
+        <v>4133</v>
       </c>
       <c r="D5" t="n">
-        <v>1848</v>
+        <v>1587</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>524</v>
+        <v>449</v>
       </c>
       <c r="C6" t="n">
-        <v>2382</v>
+        <v>2914</v>
       </c>
       <c r="D6" t="n">
-        <v>876</v>
+        <v>829</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>168</v>
+        <v>148</v>
       </c>
       <c r="C7" t="n">
-        <v>1037</v>
+        <v>1308</v>
       </c>
       <c r="D7" t="n">
-        <v>559</v>
+        <v>555</v>
       </c>
     </row>
     <row r="8">
@@ -6151,10 +6151,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C8" t="n">
-        <v>354</v>
+        <v>398</v>
       </c>
       <c r="D8" t="n">
         <v>374</v>
@@ -6168,7 +6168,7 @@
         <v>46</v>
       </c>
       <c r="C9" t="n">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D9" t="n">
         <v>283</v>
@@ -6179,10 +6179,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C10" t="n">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="D10" t="n">
         <v>238</v>
@@ -6238,7 +6238,7 @@
         <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D14" t="n">
         <v>96</v>
@@ -6308,7 +6308,7 @@
         <v>2</v>
       </c>
       <c r="C19" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D19" t="n">
         <v>26</v>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3709</v>
+        <v>4170</v>
       </c>
       <c r="C2" t="n">
-        <v>11614</v>
+        <v>8784</v>
       </c>
       <c r="D2" t="n">
-        <v>27502</v>
+        <v>31943</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2911</v>
+        <v>3407</v>
       </c>
       <c r="C3" t="n">
-        <v>6434</v>
+        <v>8272</v>
       </c>
       <c r="D3" t="n">
-        <v>15479</v>
+        <v>14197</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2167</v>
+        <v>2361</v>
       </c>
       <c r="C4" t="n">
-        <v>7259</v>
+        <v>6462</v>
       </c>
       <c r="D4" t="n">
-        <v>6750</v>
+        <v>6099</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1358</v>
+        <v>1245</v>
       </c>
       <c r="C5" t="n">
-        <v>4905</v>
+        <v>4626</v>
       </c>
       <c r="D5" t="n">
-        <v>2426</v>
+        <v>2125</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>742</v>
+        <v>650</v>
       </c>
       <c r="C6" t="n">
-        <v>3374</v>
+        <v>3502</v>
       </c>
       <c r="D6" t="n">
-        <v>1031</v>
+        <v>948</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>299</v>
+        <v>259</v>
       </c>
       <c r="C7" t="n">
-        <v>1698</v>
+        <v>2097</v>
       </c>
       <c r="D7" t="n">
-        <v>600</v>
+        <v>589</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="C8" t="n">
-        <v>688</v>
+        <v>843</v>
       </c>
       <c r="D8" t="n">
-        <v>401</v>
+        <v>400</v>
       </c>
     </row>
     <row r="9">
@@ -6476,10 +6476,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C9" t="n">
-        <v>276</v>
+        <v>297</v>
       </c>
       <c r="D9" t="n">
         <v>291</v>
@@ -6493,7 +6493,7 @@
         <v>35</v>
       </c>
       <c r="C10" t="n">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="D10" t="n">
         <v>242</v>
@@ -6507,10 +6507,10 @@
         <v>25</v>
       </c>
       <c r="C11" t="n">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D11" t="n">
-        <v>199</v>
+        <v>201</v>
       </c>
     </row>
     <row r="12">
@@ -6524,7 +6524,7 @@
         <v>113</v>
       </c>
       <c r="D12" t="n">
-        <v>157</v>
+        <v>155</v>
       </c>
     </row>
     <row r="13">
@@ -6619,7 +6619,7 @@
         <v>1</v>
       </c>
       <c r="C19" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D19" t="n">
         <v>26</v>
@@ -6633,7 +6633,7 @@
         <v>1</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D20" t="n">
         <v>16</v>

--- a/output/yearly_population_iteration_35_growth_param_0.5.xlsx
+++ b/output/yearly_population_iteration_35_growth_param_0.5.xlsx
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4312</v>
+        <v>5401</v>
       </c>
       <c r="C2" t="n">
-        <v>8506</v>
+        <v>5025</v>
       </c>
       <c r="D2" t="n">
-        <v>27548</v>
+        <v>23935</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3089</v>
+        <v>3482</v>
       </c>
       <c r="C3" t="n">
-        <v>7475</v>
+        <v>3508</v>
       </c>
       <c r="D3" t="n">
-        <v>15656</v>
+        <v>14536</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2435</v>
+        <v>2557</v>
       </c>
       <c r="C4" t="n">
-        <v>7151</v>
+        <v>4698</v>
       </c>
       <c r="D4" t="n">
-        <v>7176</v>
+        <v>7541</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1514</v>
+        <v>1754</v>
       </c>
       <c r="C5" t="n">
-        <v>5411</v>
+        <v>4433</v>
       </c>
       <c r="D5" t="n">
-        <v>2708</v>
+        <v>2943</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>826</v>
+        <v>991</v>
       </c>
       <c r="C6" t="n">
-        <v>3950</v>
+        <v>2746</v>
       </c>
       <c r="D6" t="n">
-        <v>1106</v>
+        <v>1224</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>385</v>
+        <v>476</v>
       </c>
       <c r="C7" t="n">
-        <v>2743</v>
+        <v>1441</v>
       </c>
       <c r="D7" t="n">
-        <v>639</v>
+        <v>664</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>142</v>
+        <v>179</v>
       </c>
       <c r="C8" t="n">
-        <v>1387</v>
+        <v>686</v>
       </c>
       <c r="D8" t="n">
-        <v>419</v>
+        <v>436</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>60</v>
+        <v>69</v>
       </c>
       <c r="C9" t="n">
-        <v>532</v>
+        <v>319</v>
       </c>
       <c r="D9" t="n">
-        <v>304</v>
+        <v>309</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C10" t="n">
-        <v>229</v>
+        <v>209</v>
       </c>
       <c r="D10" t="n">
-        <v>243</v>
+        <v>246</v>
       </c>
     </row>
     <row r="11">
@@ -909,10 +909,10 @@
         <v>26</v>
       </c>
       <c r="C11" t="n">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="D11" t="n">
-        <v>204</v>
+        <v>206</v>
       </c>
     </row>
     <row r="12">
@@ -920,13 +920,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C12" t="n">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="D12" t="n">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="13">
@@ -934,13 +934,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="D13" t="n">
-        <v>124</v>
+        <v>126</v>
       </c>
     </row>
     <row r="14">
@@ -948,13 +948,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C14" t="n">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="D14" t="n">
-        <v>98</v>
+        <v>101</v>
       </c>
     </row>
     <row r="15">
@@ -962,13 +962,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="D15" t="n">
-        <v>82</v>
+        <v>79</v>
       </c>
     </row>
     <row r="16">
@@ -979,7 +979,7 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D16" t="n">
         <v>65</v>
@@ -993,10 +993,10 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="18">
@@ -1007,10 +1007,10 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
     </row>
     <row r="19">
@@ -1024,7 +1024,7 @@
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="20">
@@ -1049,10 +1049,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4721</v>
+        <v>5967</v>
       </c>
       <c r="C2" t="n">
-        <v>11114</v>
+        <v>6686</v>
       </c>
       <c r="D2" t="n">
-        <v>25905</v>
+        <v>25327</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2950</v>
+        <v>3548</v>
       </c>
       <c r="C3" t="n">
-        <v>7001</v>
+        <v>3700</v>
       </c>
       <c r="D3" t="n">
-        <v>16151</v>
+        <v>14837</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2312</v>
+        <v>2561</v>
       </c>
       <c r="C4" t="n">
-        <v>7148</v>
+        <v>3972</v>
       </c>
       <c r="D4" t="n">
-        <v>8260</v>
+        <v>8380</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1683</v>
+        <v>1865</v>
       </c>
       <c r="C5" t="n">
-        <v>5998</v>
+        <v>4467</v>
       </c>
       <c r="D5" t="n">
-        <v>3243</v>
+        <v>3603</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>999</v>
+        <v>1206</v>
       </c>
       <c r="C6" t="n">
-        <v>4492</v>
+        <v>3468</v>
       </c>
       <c r="D6" t="n">
-        <v>1322</v>
+        <v>1459</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>501</v>
+        <v>634</v>
       </c>
       <c r="C7" t="n">
-        <v>3250</v>
+        <v>2041</v>
       </c>
       <c r="D7" t="n">
-        <v>690</v>
+        <v>745</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>208</v>
+        <v>268</v>
       </c>
       <c r="C8" t="n">
-        <v>1917</v>
+        <v>1011</v>
       </c>
       <c r="D8" t="n">
-        <v>444</v>
+        <v>460</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="C9" t="n">
-        <v>866</v>
+        <v>477</v>
       </c>
       <c r="D9" t="n">
-        <v>312</v>
+        <v>324</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="C10" t="n">
-        <v>339</v>
+        <v>254</v>
       </c>
       <c r="D10" t="n">
-        <v>248</v>
+        <v>249</v>
       </c>
     </row>
     <row r="11">
@@ -1220,10 +1220,10 @@
         <v>27</v>
       </c>
       <c r="C11" t="n">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="D11" t="n">
-        <v>204</v>
+        <v>209</v>
       </c>
     </row>
     <row r="12">
@@ -1231,13 +1231,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C12" t="n">
-        <v>138</v>
+        <v>144</v>
       </c>
       <c r="D12" t="n">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="13">
@@ -1245,13 +1245,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="D13" t="n">
-        <v>126</v>
+        <v>128</v>
       </c>
     </row>
     <row r="14">
@@ -1259,13 +1259,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C14" t="n">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="D14" t="n">
-        <v>98</v>
+        <v>101</v>
       </c>
     </row>
     <row r="15">
@@ -1273,13 +1273,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="D15" t="n">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="16">
@@ -1287,10 +1287,10 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="D16" t="n">
         <v>65</v>
@@ -1304,10 +1304,10 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="18">
@@ -1318,10 +1318,10 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
     </row>
     <row r="19">
@@ -1335,7 +1335,7 @@
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="20">
@@ -1360,10 +1360,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="D21" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5780</v>
+        <v>9507</v>
       </c>
       <c r="C2" t="n">
-        <v>13108</v>
+        <v>7414</v>
       </c>
       <c r="D2" t="n">
-        <v>25856</v>
+        <v>30122</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2955</v>
+        <v>3705</v>
       </c>
       <c r="C3" t="n">
-        <v>7632</v>
+        <v>4396</v>
       </c>
       <c r="D3" t="n">
-        <v>16235</v>
+        <v>15206</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2179</v>
+        <v>2531</v>
       </c>
       <c r="C4" t="n">
-        <v>6871</v>
+        <v>3728</v>
       </c>
       <c r="D4" t="n">
-        <v>8990</v>
+        <v>9036</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1711</v>
+        <v>1914</v>
       </c>
       <c r="C5" t="n">
-        <v>6268</v>
+        <v>4155</v>
       </c>
       <c r="D5" t="n">
-        <v>3787</v>
+        <v>4227</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1140</v>
+        <v>1361</v>
       </c>
       <c r="C6" t="n">
-        <v>5032</v>
+        <v>3824</v>
       </c>
       <c r="D6" t="n">
-        <v>1562</v>
+        <v>1734</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>614</v>
+        <v>776</v>
       </c>
       <c r="C7" t="n">
-        <v>3679</v>
+        <v>2641</v>
       </c>
       <c r="D7" t="n">
-        <v>756</v>
+        <v>842</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>278</v>
+        <v>365</v>
       </c>
       <c r="C8" t="n">
-        <v>2380</v>
+        <v>1414</v>
       </c>
       <c r="D8" t="n">
-        <v>470</v>
+        <v>489</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>110</v>
+        <v>144</v>
       </c>
       <c r="C9" t="n">
-        <v>1227</v>
+        <v>681</v>
       </c>
       <c r="D9" t="n">
-        <v>321</v>
+        <v>339</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="C10" t="n">
-        <v>519</v>
+        <v>339</v>
       </c>
       <c r="D10" t="n">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C11" t="n">
-        <v>232</v>
+        <v>206</v>
       </c>
       <c r="D11" t="n">
-        <v>204</v>
+        <v>211</v>
       </c>
     </row>
     <row r="12">
@@ -1542,10 +1542,10 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C12" t="n">
-        <v>151</v>
+        <v>157</v>
       </c>
       <c r="D12" t="n">
         <v>162</v>
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="D13" t="n">
-        <v>126</v>
+        <v>130</v>
       </c>
     </row>
     <row r="14">
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C14" t="n">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="D14" t="n">
-        <v>99</v>
+        <v>101</v>
       </c>
     </row>
     <row r="15">
@@ -1584,10 +1584,10 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="D15" t="n">
         <v>81</v>
@@ -1598,10 +1598,10 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="D16" t="n">
         <v>65</v>
@@ -1612,13 +1612,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="18">
@@ -1629,10 +1629,10 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
     </row>
     <row r="19">
@@ -1643,10 +1643,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D19" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="20">
@@ -1671,10 +1671,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="D21" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5333</v>
+        <v>8373</v>
       </c>
       <c r="C2" t="n">
-        <v>9228</v>
+        <v>4922</v>
       </c>
       <c r="D2" t="n">
-        <v>21619</v>
+        <v>24440</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3669</v>
+        <v>4555</v>
       </c>
       <c r="C3" t="n">
-        <v>11619</v>
+        <v>6695</v>
       </c>
       <c r="D3" t="n">
-        <v>17498</v>
+        <v>16943</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1580</v>
+        <v>1768</v>
       </c>
       <c r="C4" t="n">
-        <v>9579</v>
+        <v>6100</v>
       </c>
       <c r="D4" t="n">
-        <v>8436</v>
+        <v>8866</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1053</v>
+        <v>1257</v>
       </c>
       <c r="C5" t="n">
-        <v>4931</v>
+        <v>3747</v>
       </c>
       <c r="D5" t="n">
-        <v>2512</v>
+        <v>2876</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>567</v>
+        <v>717</v>
       </c>
       <c r="C6" t="n">
-        <v>3605</v>
+        <v>2588</v>
       </c>
       <c r="D6" t="n">
-        <v>740</v>
+        <v>825</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>256</v>
+        <v>337</v>
       </c>
       <c r="C7" t="n">
-        <v>2332</v>
+        <v>1385</v>
       </c>
       <c r="D7" t="n">
-        <v>460</v>
+        <v>479</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>101</v>
+        <v>133</v>
       </c>
       <c r="C8" t="n">
-        <v>1202</v>
+        <v>667</v>
       </c>
       <c r="D8" t="n">
-        <v>314</v>
+        <v>332</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="C9" t="n">
-        <v>508</v>
+        <v>332</v>
       </c>
       <c r="D9" t="n">
-        <v>246</v>
+        <v>247</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C10" t="n">
-        <v>227</v>
+        <v>201</v>
       </c>
       <c r="D10" t="n">
-        <v>199</v>
+        <v>206</v>
       </c>
     </row>
     <row r="11">
@@ -1839,10 +1839,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C11" t="n">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="D11" t="n">
         <v>158</v>
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="D12" t="n">
-        <v>123</v>
+        <v>127</v>
       </c>
     </row>
     <row r="13">
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C13" t="n">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="D13" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="14">
@@ -1881,10 +1881,10 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="D14" t="n">
         <v>79</v>
@@ -1895,10 +1895,10 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D15" t="n">
         <v>63</v>
@@ -1909,13 +1909,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C16" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D16" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="17">
@@ -1926,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D17" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
     </row>
     <row r="18">
@@ -1940,10 +1940,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D18" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="19">
@@ -1968,10 +1968,10 @@
         <v>8</v>
       </c>
       <c r="C20" t="n">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="D20" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3329</v>
+        <v>4822</v>
       </c>
       <c r="C2" t="n">
-        <v>4364</v>
+        <v>2396</v>
       </c>
       <c r="D2" t="n">
-        <v>14938</v>
+        <v>16490</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3746</v>
+        <v>5335</v>
       </c>
       <c r="C3" t="n">
-        <v>9640</v>
+        <v>5300</v>
       </c>
       <c r="D3" t="n">
-        <v>17045</v>
+        <v>17182</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2036</v>
+        <v>2472</v>
       </c>
       <c r="C4" t="n">
-        <v>10648</v>
+        <v>6492</v>
       </c>
       <c r="D4" t="n">
-        <v>9646</v>
+        <v>10007</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1175</v>
+        <v>1378</v>
       </c>
       <c r="C5" t="n">
-        <v>6802</v>
+        <v>4842</v>
       </c>
       <c r="D5" t="n">
-        <v>3166</v>
+        <v>3591</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>661</v>
+        <v>867</v>
       </c>
       <c r="C6" t="n">
-        <v>4259</v>
+        <v>3131</v>
       </c>
       <c r="D6" t="n">
-        <v>905</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>238</v>
+        <v>320</v>
       </c>
       <c r="C7" t="n">
-        <v>2825</v>
+        <v>1848</v>
       </c>
       <c r="D7" t="n">
-        <v>502</v>
+        <v>522</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>86</v>
+        <v>112</v>
       </c>
       <c r="C8" t="n">
-        <v>1558</v>
+        <v>884</v>
       </c>
       <c r="D8" t="n">
-        <v>323</v>
+        <v>346</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="C9" t="n">
-        <v>526</v>
+        <v>391</v>
       </c>
       <c r="D9" t="n">
-        <v>254</v>
+        <v>259</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C10" t="n">
-        <v>237</v>
+        <v>224</v>
       </c>
       <c r="D10" t="n">
-        <v>205</v>
+        <v>211</v>
       </c>
     </row>
     <row r="11">
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>161</v>
+        <v>169</v>
       </c>
       <c r="D11" t="n">
-        <v>164</v>
+        <v>167</v>
       </c>
     </row>
     <row r="12">
@@ -2164,13 +2164,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C12" t="n">
-        <v>91</v>
+        <v>99</v>
       </c>
       <c r="D12" t="n">
-        <v>129</v>
+        <v>131</v>
       </c>
     </row>
     <row r="13">
@@ -2178,13 +2178,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="D13" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="14">
@@ -2192,10 +2192,10 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D14" t="n">
         <v>61</v>
@@ -2209,10 +2209,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D15" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="16">
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D16" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
     <row r="17">
@@ -2237,10 +2237,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D17" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="18">
@@ -2265,10 +2265,10 @@
         <v>7</v>
       </c>
       <c r="C19" t="n">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="D19" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3892</v>
+        <v>4988</v>
       </c>
       <c r="C2" t="n">
-        <v>8105</v>
+        <v>4364</v>
       </c>
       <c r="D2" t="n">
-        <v>16335</v>
+        <v>15021</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3038</v>
+        <v>4288</v>
       </c>
       <c r="C3" t="n">
-        <v>6430</v>
+        <v>3426</v>
       </c>
       <c r="D3" t="n">
-        <v>15776</v>
+        <v>15900</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2337</v>
+        <v>3218</v>
       </c>
       <c r="C4" t="n">
-        <v>10054</v>
+        <v>5750</v>
       </c>
       <c r="D4" t="n">
-        <v>10396</v>
+        <v>10942</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1358</v>
+        <v>1644</v>
       </c>
       <c r="C5" t="n">
-        <v>8358</v>
+        <v>5595</v>
       </c>
       <c r="D5" t="n">
-        <v>4065</v>
+        <v>4528</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>790</v>
+        <v>999</v>
       </c>
       <c r="C6" t="n">
-        <v>5293</v>
+        <v>3888</v>
       </c>
       <c r="D6" t="n">
-        <v>1218</v>
+        <v>1414</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>349</v>
+        <v>479</v>
       </c>
       <c r="C7" t="n">
-        <v>3441</v>
+        <v>2443</v>
       </c>
       <c r="D7" t="n">
-        <v>557</v>
+        <v>592</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>120</v>
+        <v>165</v>
       </c>
       <c r="C8" t="n">
-        <v>2056</v>
+        <v>1298</v>
       </c>
       <c r="D8" t="n">
-        <v>340</v>
+        <v>370</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>46</v>
+        <v>58</v>
       </c>
       <c r="C9" t="n">
-        <v>895</v>
+        <v>591</v>
       </c>
       <c r="D9" t="n">
-        <v>258</v>
+        <v>266</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="C10" t="n">
-        <v>335</v>
+        <v>285</v>
       </c>
       <c r="D10" t="n">
-        <v>209</v>
+        <v>216</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>185</v>
+        <v>191</v>
       </c>
       <c r="D11" t="n">
-        <v>167</v>
+        <v>170</v>
       </c>
     </row>
     <row r="12">
@@ -2475,13 +2475,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C12" t="n">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="D12" t="n">
-        <v>131</v>
+        <v>133</v>
       </c>
     </row>
     <row r="13">
@@ -2489,13 +2489,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>68</v>
+        <v>77</v>
       </c>
       <c r="D13" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="14">
@@ -2506,10 +2506,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D14" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="15">
@@ -2520,10 +2520,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D15" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
     </row>
     <row r="16">
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="D16" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
     </row>
     <row r="17">
@@ -2548,10 +2548,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D17" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="18">
@@ -2562,7 +2562,7 @@
         <v>6</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D18" t="n">
         <v>13</v>
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="D19" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2328</v>
+        <v>2888</v>
       </c>
       <c r="C2" t="n">
-        <v>4011</v>
+        <v>1965</v>
       </c>
       <c r="D2" t="n">
-        <v>11537</v>
+        <v>10374</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3144</v>
+        <v>4342</v>
       </c>
       <c r="C3" t="n">
-        <v>6787</v>
+        <v>3641</v>
       </c>
       <c r="D3" t="n">
-        <v>15501</v>
+        <v>15419</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2551</v>
+        <v>3578</v>
       </c>
       <c r="C4" t="n">
-        <v>9731</v>
+        <v>5379</v>
       </c>
       <c r="D4" t="n">
-        <v>11070</v>
+        <v>11610</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1402</v>
+        <v>1728</v>
       </c>
       <c r="C5" t="n">
-        <v>10031</v>
+        <v>6472</v>
       </c>
       <c r="D5" t="n">
-        <v>4167</v>
+        <v>4905</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>629</v>
+        <v>867</v>
       </c>
       <c r="C6" t="n">
-        <v>6193</v>
+        <v>4775</v>
       </c>
       <c r="D6" t="n">
-        <v>1186</v>
+        <v>1386</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>110</v>
+        <v>152</v>
       </c>
       <c r="C7" t="n">
-        <v>3622</v>
+        <v>2504</v>
       </c>
       <c r="D7" t="n">
-        <v>556</v>
+        <v>596</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="C8" t="n">
-        <v>1461</v>
+        <v>998</v>
       </c>
       <c r="D8" t="n">
-        <v>366</v>
+        <v>386</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="C9" t="n">
-        <v>328</v>
+        <v>279</v>
       </c>
       <c r="D9" t="n">
-        <v>278</v>
+        <v>292</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>181</v>
+        <v>187</v>
       </c>
       <c r="D10" t="n">
-        <v>163</v>
+        <v>166</v>
       </c>
     </row>
     <row r="11">
@@ -2772,13 +2772,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C11" t="n">
-        <v>107</v>
+        <v>117</v>
       </c>
       <c r="D11" t="n">
-        <v>128</v>
+        <v>130</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>66</v>
+        <v>75</v>
       </c>
       <c r="D12" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="13">
@@ -2803,10 +2803,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D13" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="14">
@@ -2817,10 +2817,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D14" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="15">
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="D15" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="16">
@@ -2845,10 +2845,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D16" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="17">
@@ -2859,7 +2859,7 @@
         <v>5</v>
       </c>
       <c r="C17" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D17" t="n">
         <v>12</v>
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="D18" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2533</v>
+        <v>3877</v>
       </c>
       <c r="C2" t="n">
-        <v>7947</v>
+        <v>4470</v>
       </c>
       <c r="D2" t="n">
-        <v>12552</v>
+        <v>13772</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2413</v>
+        <v>3176</v>
       </c>
       <c r="C3" t="n">
-        <v>4993</v>
+        <v>2530</v>
       </c>
       <c r="D3" t="n">
-        <v>13976</v>
+        <v>13779</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2425</v>
+        <v>3437</v>
       </c>
       <c r="C4" t="n">
-        <v>8293</v>
+        <v>4416</v>
       </c>
       <c r="D4" t="n">
-        <v>11414</v>
+        <v>11878</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1645</v>
+        <v>2197</v>
       </c>
       <c r="C5" t="n">
-        <v>9791</v>
+        <v>5885</v>
       </c>
       <c r="D5" t="n">
-        <v>5074</v>
+        <v>5785</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>824</v>
+        <v>1095</v>
       </c>
       <c r="C6" t="n">
-        <v>7711</v>
+        <v>5572</v>
       </c>
       <c r="D6" t="n">
-        <v>1542</v>
+        <v>1888</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>226</v>
+        <v>340</v>
       </c>
       <c r="C7" t="n">
-        <v>4613</v>
+        <v>3462</v>
       </c>
       <c r="D7" t="n">
-        <v>624</v>
+        <v>690</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>54</v>
+        <v>73</v>
       </c>
       <c r="C8" t="n">
-        <v>2230</v>
+        <v>1602</v>
       </c>
       <c r="D8" t="n">
-        <v>386</v>
+        <v>410</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="C9" t="n">
-        <v>681</v>
+        <v>523</v>
       </c>
       <c r="D9" t="n">
-        <v>288</v>
+        <v>301</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="D10" t="n">
-        <v>169</v>
+        <v>177</v>
       </c>
     </row>
     <row r="11">
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C11" t="n">
-        <v>125</v>
+        <v>139</v>
       </c>
       <c r="D11" t="n">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="D12" t="n">
-        <v>97</v>
+        <v>100</v>
       </c>
     </row>
     <row r="13">
@@ -3114,10 +3114,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="D13" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="D14" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
     </row>
     <row r="15">
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="D15" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
     <row r="16">
@@ -3159,7 +3159,7 @@
         <v>58</v>
       </c>
       <c r="D16" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="17">
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="D17" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="18">
@@ -3184,7 +3184,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D18" t="n">
         <v>2</v>
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1697</v>
+        <v>2660</v>
       </c>
       <c r="C2" t="n">
-        <v>4848</v>
+        <v>2523</v>
       </c>
       <c r="D2" t="n">
-        <v>9462</v>
+        <v>10943</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2148</v>
+        <v>2987</v>
       </c>
       <c r="C3" t="n">
-        <v>5546</v>
+        <v>3040</v>
       </c>
       <c r="D3" t="n">
-        <v>13078</v>
+        <v>13138</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2228</v>
+        <v>3091</v>
       </c>
       <c r="C4" t="n">
-        <v>7092</v>
+        <v>3612</v>
       </c>
       <c r="D4" t="n">
-        <v>11496</v>
+        <v>11886</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1766</v>
+        <v>2428</v>
       </c>
       <c r="C5" t="n">
-        <v>9459</v>
+        <v>5424</v>
       </c>
       <c r="D5" t="n">
-        <v>5686</v>
+        <v>6366</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>949</v>
+        <v>1314</v>
       </c>
       <c r="C6" t="n">
-        <v>8620</v>
+        <v>5907</v>
       </c>
       <c r="D6" t="n">
-        <v>1825</v>
+        <v>2294</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>202</v>
+        <v>332</v>
       </c>
       <c r="C7" t="n">
-        <v>5550</v>
+        <v>4256</v>
       </c>
       <c r="D7" t="n">
-        <v>698</v>
+        <v>781</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>44</v>
+        <v>61</v>
       </c>
       <c r="C8" t="n">
-        <v>2821</v>
+        <v>2086</v>
       </c>
       <c r="D8" t="n">
-        <v>395</v>
+        <v>433</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="C9" t="n">
-        <v>717</v>
+        <v>650</v>
       </c>
       <c r="D9" t="n">
-        <v>285</v>
+        <v>297</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C10" t="n">
-        <v>223</v>
+        <v>230</v>
       </c>
       <c r="D10" t="n">
-        <v>173</v>
+        <v>182</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>122</v>
+        <v>139</v>
       </c>
       <c r="D11" t="n">
-        <v>134</v>
+        <v>136</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>73</v>
+        <v>84</v>
       </c>
       <c r="D12" t="n">
-        <v>91</v>
+        <v>93</v>
       </c>
     </row>
     <row r="13">
@@ -3425,10 +3425,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="D13" t="n">
-        <v>61</v>
+        <v>64</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="D14" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
     </row>
     <row r="15">
@@ -3456,7 +3456,7 @@
         <v>56</v>
       </c>
       <c r="D15" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="16">
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="D16" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="17">
@@ -3481,7 +3481,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D17" t="n">
         <v>1</v>
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2034</v>
+        <v>3947</v>
       </c>
       <c r="C2" t="n">
-        <v>5147</v>
+        <v>6691</v>
       </c>
       <c r="D2" t="n">
-        <v>11291</v>
+        <v>15461</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1683</v>
+        <v>2407</v>
       </c>
       <c r="C3" t="n">
-        <v>4770</v>
+        <v>2495</v>
       </c>
       <c r="D3" t="n">
-        <v>11856</v>
+        <v>11995</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1932</v>
+        <v>2678</v>
       </c>
       <c r="C4" t="n">
-        <v>6267</v>
+        <v>3278</v>
       </c>
       <c r="D4" t="n">
-        <v>11359</v>
+        <v>11716</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1747</v>
+        <v>2424</v>
       </c>
       <c r="C5" t="n">
-        <v>8353</v>
+        <v>4580</v>
       </c>
       <c r="D5" t="n">
-        <v>6183</v>
+        <v>6967</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1122</v>
+        <v>1590</v>
       </c>
       <c r="C6" t="n">
-        <v>8857</v>
+        <v>5660</v>
       </c>
       <c r="D6" t="n">
-        <v>2283</v>
+        <v>2811</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>371</v>
+        <v>588</v>
       </c>
       <c r="C7" t="n">
-        <v>6685</v>
+        <v>4901</v>
       </c>
       <c r="D7" t="n">
-        <v>823</v>
+        <v>965</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>75</v>
+        <v>126</v>
       </c>
       <c r="C8" t="n">
-        <v>3702</v>
+        <v>2913</v>
       </c>
       <c r="D8" t="n">
-        <v>423</v>
+        <v>469</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="C9" t="n">
-        <v>1362</v>
+        <v>1148</v>
       </c>
       <c r="D9" t="n">
-        <v>292</v>
+        <v>308</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C10" t="n">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="D10" t="n">
-        <v>182</v>
+        <v>191</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>147</v>
+        <v>166</v>
       </c>
       <c r="D11" t="n">
-        <v>135</v>
+        <v>140</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>84</v>
+        <v>99</v>
       </c>
       <c r="D12" t="n">
-        <v>93</v>
+        <v>95</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="D13" t="n">
-        <v>62</v>
+        <v>65</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="D14" t="n">
-        <v>35</v>
+        <v>39</v>
       </c>
     </row>
     <row r="15">
@@ -3764,10 +3764,10 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D15" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="16">
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>64</v>
+        <v>72</v>
       </c>
       <c r="D16" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4220</v>
+        <v>5335</v>
       </c>
       <c r="C2" t="n">
-        <v>15810</v>
+        <v>4228</v>
       </c>
       <c r="D2" t="n">
-        <v>6932</v>
+        <v>7494</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1485</v>
+        <v>2763</v>
       </c>
       <c r="C2" t="n">
-        <v>3047</v>
+        <v>3693</v>
       </c>
       <c r="D2" t="n">
-        <v>8401</v>
+        <v>11379</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2238</v>
+        <v>3282</v>
       </c>
       <c r="C3" t="n">
-        <v>5343</v>
+        <v>3743</v>
       </c>
       <c r="D3" t="n">
-        <v>12886</v>
+        <v>13179</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2585</v>
+        <v>3588</v>
       </c>
       <c r="C4" t="n">
-        <v>9129</v>
+        <v>4777</v>
       </c>
       <c r="D4" t="n">
-        <v>11516</v>
+        <v>12177</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1052</v>
+        <v>1581</v>
       </c>
       <c r="C5" t="n">
-        <v>12416</v>
+        <v>7404</v>
       </c>
       <c r="D5" t="n">
-        <v>5592</v>
+        <v>6432</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>342</v>
+        <v>543</v>
       </c>
       <c r="C6" t="n">
-        <v>8026</v>
+        <v>6023</v>
       </c>
       <c r="D6" t="n">
-        <v>1806</v>
+        <v>2218</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>69</v>
+        <v>116</v>
       </c>
       <c r="C7" t="n">
-        <v>3627</v>
+        <v>2854</v>
       </c>
       <c r="D7" t="n">
-        <v>511</v>
+        <v>592</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="C8" t="n">
-        <v>1334</v>
+        <v>1125</v>
       </c>
       <c r="D8" t="n">
-        <v>286</v>
+        <v>301</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C9" t="n">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="D9" t="n">
-        <v>178</v>
+        <v>187</v>
       </c>
     </row>
     <row r="10">
@@ -4316,10 +4316,10 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>144</v>
+        <v>162</v>
       </c>
       <c r="D10" t="n">
-        <v>132</v>
+        <v>137</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>82</v>
+        <v>97</v>
       </c>
       <c r="D11" t="n">
-        <v>91</v>
+        <v>93</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="D12" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="D13" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
     </row>
     <row r="14">
@@ -4372,10 +4372,10 @@
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D14" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="15">
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>62</v>
+        <v>70</v>
       </c>
       <c r="D15" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="16">
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6115</v>
+        <v>6700</v>
       </c>
       <c r="C2" t="n">
-        <v>9522</v>
+        <v>6119</v>
       </c>
       <c r="D2" t="n">
-        <v>14844</v>
+        <v>22957</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1794</v>
+        <v>2267</v>
       </c>
       <c r="C3" t="n">
-        <v>7968</v>
+        <v>2164</v>
       </c>
       <c r="D3" t="n">
-        <v>1803</v>
+        <v>1958</v>
       </c>
     </row>
     <row r="4">
@@ -4543,7 +4543,7 @@
         <v>79</v>
       </c>
       <c r="C4" t="n">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="D4" t="n">
         <v>1538</v>
@@ -4554,10 +4554,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="C5" t="n">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="D5" t="n">
         <v>1161</v>
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="C6" t="n">
         <v>459</v>
       </c>
       <c r="D6" t="n">
-        <v>816</v>
+        <v>808</v>
       </c>
     </row>
     <row r="7">
@@ -4588,7 +4588,7 @@
         <v>350</v>
       </c>
       <c r="D7" t="n">
-        <v>538</v>
+        <v>546</v>
       </c>
     </row>
     <row r="8">
@@ -4655,7 +4655,7 @@
         <v>26</v>
       </c>
       <c r="C12" t="n">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D12" t="n">
         <v>199</v>
@@ -4669,7 +4669,7 @@
         <v>19</v>
       </c>
       <c r="C13" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D13" t="n">
         <v>170</v>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4484</v>
+        <v>4267</v>
       </c>
       <c r="C2" t="n">
-        <v>5727</v>
+        <v>4067</v>
       </c>
       <c r="D2" t="n">
-        <v>24938</v>
+        <v>20925</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3243</v>
+        <v>3680</v>
       </c>
       <c r="C3" t="n">
-        <v>7629</v>
+        <v>3796</v>
       </c>
       <c r="D3" t="n">
-        <v>3861</v>
+        <v>5341</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>813</v>
+        <v>1018</v>
       </c>
       <c r="C4" t="n">
-        <v>4712</v>
+        <v>1311</v>
       </c>
       <c r="D4" t="n">
-        <v>1544</v>
+        <v>1575</v>
       </c>
     </row>
     <row r="5">
@@ -4868,10 +4868,10 @@
         <v>125</v>
       </c>
       <c r="C5" t="n">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="D5" t="n">
-        <v>1198</v>
+        <v>1186</v>
       </c>
     </row>
     <row r="6">
@@ -4882,10 +4882,10 @@
         <v>185</v>
       </c>
       <c r="C6" t="n">
-        <v>406</v>
+        <v>411</v>
       </c>
       <c r="D6" t="n">
-        <v>859</v>
+        <v>864</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C7" t="n">
         <v>409</v>
       </c>
       <c r="D7" t="n">
-        <v>584</v>
+        <v>589</v>
       </c>
     </row>
     <row r="8">
@@ -4907,13 +4907,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C8" t="n">
         <v>307</v>
       </c>
       <c r="D8" t="n">
-        <v>439</v>
+        <v>441</v>
       </c>
     </row>
     <row r="9">
@@ -4921,7 +4921,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C9" t="n">
         <v>232</v>
@@ -4935,10 +4935,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C10" t="n">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="D10" t="n">
         <v>352</v>
@@ -4966,7 +4966,7 @@
         <v>28</v>
       </c>
       <c r="C12" t="n">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D12" t="n">
         <v>206</v>
@@ -4994,7 +4994,7 @@
         <v>15</v>
       </c>
       <c r="C14" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D14" t="n">
         <v>146</v>
@@ -5005,7 +5005,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C15" t="n">
         <v>74</v>
@@ -5022,10 +5022,10 @@
         <v>13</v>
       </c>
       <c r="C16" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D16" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="17">
@@ -5039,7 +5039,7 @@
         <v>68</v>
       </c>
       <c r="D17" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="18">
@@ -5050,7 +5050,7 @@
         <v>11</v>
       </c>
       <c r="C18" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D18" t="n">
         <v>59</v>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4255</v>
+        <v>4767</v>
       </c>
       <c r="C2" t="n">
-        <v>6755</v>
+        <v>6252</v>
       </c>
       <c r="D2" t="n">
-        <v>25943</v>
+        <v>24627</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3158</v>
+        <v>3271</v>
       </c>
       <c r="C3" t="n">
-        <v>5733</v>
+        <v>3413</v>
       </c>
       <c r="D3" t="n">
-        <v>6955</v>
+        <v>7449</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1693</v>
+        <v>1987</v>
       </c>
       <c r="C4" t="n">
-        <v>6238</v>
+        <v>2691</v>
       </c>
       <c r="D4" t="n">
-        <v>1941</v>
+        <v>2250</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>389</v>
+        <v>478</v>
       </c>
       <c r="C5" t="n">
-        <v>2629</v>
+        <v>810</v>
       </c>
       <c r="D5" t="n">
-        <v>1224</v>
+        <v>1209</v>
       </c>
     </row>
     <row r="6">
@@ -5193,10 +5193,10 @@
         <v>147</v>
       </c>
       <c r="C6" t="n">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="D6" t="n">
-        <v>897</v>
+        <v>910</v>
       </c>
     </row>
     <row r="7">
@@ -5207,10 +5207,10 @@
         <v>160</v>
       </c>
       <c r="C7" t="n">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="D7" t="n">
-        <v>626</v>
+        <v>625</v>
       </c>
     </row>
     <row r="8">
@@ -5221,10 +5221,10 @@
         <v>124</v>
       </c>
       <c r="C8" t="n">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="D8" t="n">
-        <v>454</v>
+        <v>462</v>
       </c>
     </row>
     <row r="9">
@@ -5235,10 +5235,10 @@
         <v>91</v>
       </c>
       <c r="C9" t="n">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="D9" t="n">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="10">
@@ -5252,7 +5252,7 @@
         <v>210</v>
       </c>
       <c r="D10" t="n">
-        <v>350</v>
+        <v>346</v>
       </c>
     </row>
     <row r="11">
@@ -5263,10 +5263,10 @@
         <v>47</v>
       </c>
       <c r="C11" t="n">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="D11" t="n">
-        <v>276</v>
+        <v>280</v>
       </c>
     </row>
     <row r="12">
@@ -5277,10 +5277,10 @@
         <v>31</v>
       </c>
       <c r="C12" t="n">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D12" t="n">
-        <v>213</v>
+        <v>211</v>
       </c>
     </row>
     <row r="13">
@@ -5291,10 +5291,10 @@
         <v>21</v>
       </c>
       <c r="C13" t="n">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D13" t="n">
-        <v>173</v>
+        <v>175</v>
       </c>
     </row>
     <row r="14">
@@ -5316,13 +5316,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C15" t="n">
         <v>77</v>
       </c>
       <c r="D15" t="n">
-        <v>122</v>
+        <v>120</v>
       </c>
     </row>
     <row r="16">
@@ -5333,7 +5333,7 @@
         <v>12</v>
       </c>
       <c r="C16" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D16" t="n">
         <v>99</v>
@@ -5350,7 +5350,7 @@
         <v>68</v>
       </c>
       <c r="D17" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="18">
@@ -5375,7 +5375,7 @@
         <v>10</v>
       </c>
       <c r="C19" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D19" t="n">
         <v>41</v>
@@ -5403,10 +5403,10 @@
         <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="D21" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4452</v>
+        <v>5725</v>
       </c>
       <c r="C2" t="n">
-        <v>9106</v>
+        <v>9181</v>
       </c>
       <c r="D2" t="n">
-        <v>31388</v>
+        <v>28892</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3018</v>
+        <v>3269</v>
       </c>
       <c r="C3" t="n">
-        <v>5448</v>
+        <v>4292</v>
       </c>
       <c r="D3" t="n">
-        <v>9351</v>
+        <v>9535</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2045</v>
+        <v>2224</v>
       </c>
       <c r="C4" t="n">
-        <v>5841</v>
+        <v>2997</v>
       </c>
       <c r="D4" t="n">
-        <v>2796</v>
+        <v>3108</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>839</v>
+        <v>1026</v>
       </c>
       <c r="C5" t="n">
-        <v>4410</v>
+        <v>1786</v>
       </c>
       <c r="D5" t="n">
-        <v>1310</v>
+        <v>1362</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>234</v>
+        <v>271</v>
       </c>
       <c r="C6" t="n">
-        <v>1436</v>
+        <v>557</v>
       </c>
       <c r="D6" t="n">
-        <v>929</v>
+        <v>949</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C7" t="n">
-        <v>356</v>
+        <v>351</v>
       </c>
       <c r="D7" t="n">
-        <v>664</v>
+        <v>659</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C8" t="n">
-        <v>376</v>
+        <v>382</v>
       </c>
       <c r="D8" t="n">
-        <v>471</v>
+        <v>484</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C9" t="n">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="D9" t="n">
-        <v>380</v>
+        <v>378</v>
       </c>
     </row>
     <row r="10">
@@ -5560,7 +5560,7 @@
         <v>70</v>
       </c>
       <c r="C10" t="n">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="D10" t="n">
         <v>346</v>
@@ -5574,10 +5574,10 @@
         <v>50</v>
       </c>
       <c r="C11" t="n">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="D11" t="n">
-        <v>284</v>
+        <v>286</v>
       </c>
     </row>
     <row r="12">
@@ -5585,13 +5585,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C12" t="n">
         <v>159</v>
       </c>
       <c r="D12" t="n">
-        <v>219</v>
+        <v>216</v>
       </c>
     </row>
     <row r="13">
@@ -5602,10 +5602,10 @@
         <v>22</v>
       </c>
       <c r="C13" t="n">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D13" t="n">
-        <v>174</v>
+        <v>178</v>
       </c>
     </row>
     <row r="14">
@@ -5616,10 +5616,10 @@
         <v>15</v>
       </c>
       <c r="C14" t="n">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="D14" t="n">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="15">
@@ -5644,10 +5644,10 @@
         <v>11</v>
       </c>
       <c r="C16" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D16" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="17">
@@ -5658,10 +5658,10 @@
         <v>10</v>
       </c>
       <c r="C17" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D17" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
     </row>
     <row r="18">
@@ -5689,7 +5689,7 @@
         <v>62</v>
       </c>
       <c r="D19" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="20">
@@ -5714,10 +5714,10 @@
         <v>21</v>
       </c>
       <c r="C21" t="n">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6545</v>
+        <v>5892</v>
       </c>
       <c r="C2" t="n">
-        <v>11461</v>
+        <v>8186</v>
       </c>
       <c r="D2" t="n">
-        <v>26743</v>
+        <v>25512</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2687</v>
+        <v>3260</v>
       </c>
       <c r="C3" t="n">
-        <v>5943</v>
+        <v>5598</v>
       </c>
       <c r="D3" t="n">
-        <v>11163</v>
+        <v>11106</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1563</v>
+        <v>1716</v>
       </c>
       <c r="C4" t="n">
-        <v>4557</v>
+        <v>3053</v>
       </c>
       <c r="D4" t="n">
-        <v>3326</v>
+        <v>3627</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>734</v>
+        <v>848</v>
       </c>
       <c r="C5" t="n">
-        <v>3742</v>
+        <v>1773</v>
       </c>
       <c r="D5" t="n">
-        <v>1236</v>
+        <v>1329</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>248</v>
+        <v>309</v>
       </c>
       <c r="C6" t="n">
-        <v>1926</v>
+        <v>788</v>
       </c>
       <c r="D6" t="n">
-        <v>746</v>
+        <v>768</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="C7" t="n">
-        <v>557</v>
+        <v>290</v>
       </c>
       <c r="D7" t="n">
-        <v>518</v>
+        <v>520</v>
       </c>
     </row>
     <row r="8">
@@ -5843,10 +5843,10 @@
         <v>58</v>
       </c>
       <c r="C8" t="n">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="D8" t="n">
-        <v>352</v>
+        <v>364</v>
       </c>
     </row>
     <row r="9">
@@ -5857,10 +5857,10 @@
         <v>44</v>
       </c>
       <c r="C9" t="n">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="D9" t="n">
-        <v>272</v>
+        <v>270</v>
       </c>
     </row>
     <row r="10">
@@ -5871,10 +5871,10 @@
         <v>30</v>
       </c>
       <c r="C10" t="n">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D10" t="n">
-        <v>235</v>
+        <v>237</v>
       </c>
     </row>
     <row r="11">
@@ -5885,10 +5885,10 @@
         <v>21</v>
       </c>
       <c r="C11" t="n">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D11" t="n">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="12">
@@ -5896,13 +5896,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C12" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D12" t="n">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="13">
@@ -5913,10 +5913,10 @@
         <v>9</v>
       </c>
       <c r="C13" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D13" t="n">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="14">
@@ -5927,10 +5927,10 @@
         <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D14" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="15">
@@ -5941,7 +5941,7 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D15" t="n">
         <v>79</v>
@@ -5958,7 +5958,7 @@
         <v>38</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="17">
@@ -5969,10 +5969,10 @@
         <v>3</v>
       </c>
       <c r="C17" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D17" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
     </row>
     <row r="18">
@@ -6028,7 +6028,7 @@
         <v>75</v>
       </c>
       <c r="D21" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4508</v>
+        <v>4548</v>
       </c>
       <c r="C2" t="n">
-        <v>10899</v>
+        <v>4296</v>
       </c>
       <c r="D2" t="n">
-        <v>27116</v>
+        <v>25058</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3792</v>
+        <v>3803</v>
       </c>
       <c r="C3" t="n">
-        <v>7818</v>
+        <v>6125</v>
       </c>
       <c r="D3" t="n">
-        <v>12958</v>
+        <v>12806</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1833</v>
+        <v>2173</v>
       </c>
       <c r="C4" t="n">
-        <v>5230</v>
+        <v>4553</v>
       </c>
       <c r="D4" t="n">
-        <v>4804</v>
+        <v>5096</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1018</v>
+        <v>1152</v>
       </c>
       <c r="C5" t="n">
-        <v>4133</v>
+        <v>2497</v>
       </c>
       <c r="D5" t="n">
-        <v>1587</v>
+        <v>1751</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>449</v>
+        <v>540</v>
       </c>
       <c r="C6" t="n">
-        <v>2914</v>
+        <v>1345</v>
       </c>
       <c r="D6" t="n">
-        <v>829</v>
+        <v>857</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>148</v>
+        <v>181</v>
       </c>
       <c r="C7" t="n">
-        <v>1308</v>
+        <v>572</v>
       </c>
       <c r="D7" t="n">
-        <v>555</v>
+        <v>563</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="C8" t="n">
-        <v>398</v>
+        <v>257</v>
       </c>
       <c r="D8" t="n">
-        <v>374</v>
+        <v>389</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C9" t="n">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="D9" t="n">
-        <v>283</v>
+        <v>281</v>
       </c>
     </row>
     <row r="10">
@@ -6182,10 +6182,10 @@
         <v>33</v>
       </c>
       <c r="C10" t="n">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="D10" t="n">
-        <v>238</v>
+        <v>240</v>
       </c>
     </row>
     <row r="11">
@@ -6196,10 +6196,10 @@
         <v>23</v>
       </c>
       <c r="C11" t="n">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="D11" t="n">
-        <v>197</v>
+        <v>199</v>
       </c>
     </row>
     <row r="12">
@@ -6207,13 +6207,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C12" t="n">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D12" t="n">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="13">
@@ -6221,13 +6221,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C13" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="D13" t="n">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="14">
@@ -6235,13 +6235,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D14" t="n">
-        <v>96</v>
+        <v>98</v>
       </c>
     </row>
     <row r="15">
@@ -6252,10 +6252,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D15" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="16">
@@ -6266,7 +6266,7 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D16" t="n">
         <v>64</v>
@@ -6280,10 +6280,10 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D17" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
     </row>
     <row r="18">
@@ -6311,7 +6311,7 @@
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="20">
@@ -6336,10 +6336,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D21" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4170</v>
+        <v>5164</v>
       </c>
       <c r="C2" t="n">
-        <v>8784</v>
+        <v>3640</v>
       </c>
       <c r="D2" t="n">
-        <v>31943</v>
+        <v>24809</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3407</v>
+        <v>3439</v>
       </c>
       <c r="C3" t="n">
-        <v>8272</v>
+        <v>4414</v>
       </c>
       <c r="D3" t="n">
-        <v>14197</v>
+        <v>13844</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2361</v>
+        <v>2582</v>
       </c>
       <c r="C4" t="n">
-        <v>6462</v>
+        <v>5363</v>
       </c>
       <c r="D4" t="n">
-        <v>6099</v>
+        <v>6372</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1245</v>
+        <v>1452</v>
       </c>
       <c r="C5" t="n">
-        <v>4626</v>
+        <v>3589</v>
       </c>
       <c r="D5" t="n">
-        <v>2125</v>
+        <v>2340</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>650</v>
+        <v>774</v>
       </c>
       <c r="C6" t="n">
-        <v>3502</v>
+        <v>1948</v>
       </c>
       <c r="D6" t="n">
-        <v>948</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>259</v>
+        <v>318</v>
       </c>
       <c r="C7" t="n">
-        <v>2097</v>
+        <v>975</v>
       </c>
       <c r="D7" t="n">
-        <v>589</v>
+        <v>603</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>92</v>
+        <v>110</v>
       </c>
       <c r="C8" t="n">
-        <v>843</v>
+        <v>420</v>
       </c>
       <c r="D8" t="n">
-        <v>400</v>
+        <v>415</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C9" t="n">
-        <v>297</v>
+        <v>234</v>
       </c>
       <c r="D9" t="n">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="10">
@@ -6493,10 +6493,10 @@
         <v>35</v>
       </c>
       <c r="C10" t="n">
-        <v>186</v>
+        <v>193</v>
       </c>
       <c r="D10" t="n">
-        <v>242</v>
+        <v>244</v>
       </c>
     </row>
     <row r="11">
@@ -6507,10 +6507,10 @@
         <v>25</v>
       </c>
       <c r="C11" t="n">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="D11" t="n">
-        <v>201</v>
+        <v>203</v>
       </c>
     </row>
     <row r="12">
@@ -6518,10 +6518,10 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C12" t="n">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D12" t="n">
         <v>155</v>
@@ -6532,13 +6532,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="D13" t="n">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="14">
@@ -6546,13 +6546,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="D14" t="n">
-        <v>97</v>
+        <v>100</v>
       </c>
     </row>
     <row r="15">
@@ -6563,10 +6563,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D15" t="n">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="16">
@@ -6577,10 +6577,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="17">
@@ -6591,10 +6591,10 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="18">
@@ -6605,10 +6605,10 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19">
@@ -6622,7 +6622,7 @@
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="20">
@@ -6647,10 +6647,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_population_iteration_35_growth_param_0.5.xlsx
+++ b/output/yearly_population_iteration_35_growth_param_0.5.xlsx
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5401</v>
+        <v>1040</v>
       </c>
       <c r="C2" t="n">
-        <v>5025</v>
+        <v>2994</v>
       </c>
       <c r="D2" t="n">
-        <v>23935</v>
+        <v>19064</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3482</v>
+        <v>1998</v>
       </c>
       <c r="C3" t="n">
-        <v>3508</v>
+        <v>6359</v>
       </c>
       <c r="D3" t="n">
-        <v>14536</v>
+        <v>16588</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2557</v>
+        <v>1555</v>
       </c>
       <c r="C4" t="n">
-        <v>4698</v>
+        <v>6958</v>
       </c>
       <c r="D4" t="n">
-        <v>7541</v>
+        <v>6447</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1754</v>
+        <v>804</v>
       </c>
       <c r="C5" t="n">
-        <v>4433</v>
+        <v>3487</v>
       </c>
       <c r="D5" t="n">
-        <v>2943</v>
+        <v>1969</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>991</v>
+        <v>321</v>
       </c>
       <c r="C6" t="n">
-        <v>2746</v>
+        <v>1365</v>
       </c>
       <c r="D6" t="n">
-        <v>1224</v>
+        <v>732</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>476</v>
+        <v>107</v>
       </c>
       <c r="C7" t="n">
-        <v>1441</v>
+        <v>589</v>
       </c>
       <c r="D7" t="n">
-        <v>664</v>
+        <v>494</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>179</v>
+        <v>74</v>
       </c>
       <c r="C8" t="n">
-        <v>686</v>
+        <v>343</v>
       </c>
       <c r="D8" t="n">
-        <v>436</v>
+        <v>369</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>69</v>
+        <v>54</v>
       </c>
       <c r="C9" t="n">
+        <v>289</v>
+      </c>
+      <c r="D9" t="n">
         <v>319</v>
-      </c>
-      <c r="D9" t="n">
-        <v>309</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="C10" t="n">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="D10" t="n">
-        <v>246</v>
+        <v>269</v>
       </c>
     </row>
     <row r="11">
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="C11" t="n">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="D11" t="n">
-        <v>206</v>
+        <v>211</v>
       </c>
     </row>
     <row r="12">
@@ -920,13 +920,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="C12" t="n">
-        <v>129</v>
+        <v>111</v>
       </c>
       <c r="D12" t="n">
-        <v>158</v>
+        <v>174</v>
       </c>
     </row>
     <row r="13">
@@ -934,13 +934,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C13" t="n">
-        <v>99</v>
+        <v>78</v>
       </c>
       <c r="D13" t="n">
-        <v>126</v>
+        <v>139</v>
       </c>
     </row>
     <row r="14">
@@ -948,13 +948,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>78</v>
+        <v>66</v>
       </c>
       <c r="D14" t="n">
-        <v>101</v>
+        <v>89</v>
       </c>
     </row>
     <row r="15">
@@ -965,10 +965,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>72</v>
       </c>
     </row>
     <row r="16">
@@ -976,13 +976,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C16" t="n">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>53</v>
       </c>
     </row>
     <row r="17">
@@ -990,13 +990,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C17" t="n">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>37</v>
       </c>
     </row>
     <row r="18">
@@ -1004,13 +1004,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C18" t="n">
-        <v>34</v>
+        <v>49</v>
       </c>
       <c r="D18" t="n">
-        <v>40</v>
+        <v>22</v>
       </c>
     </row>
     <row r="19">
@@ -1018,13 +1018,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>142</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>5</v>
       </c>
     </row>
     <row r="20">
@@ -1035,10 +1035,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>99</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5967</v>
+        <v>967</v>
       </c>
       <c r="C2" t="n">
-        <v>6686</v>
+        <v>5262</v>
       </c>
       <c r="D2" t="n">
-        <v>25327</v>
+        <v>24875</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3548</v>
+        <v>1301</v>
       </c>
       <c r="C3" t="n">
-        <v>3700</v>
+        <v>3977</v>
       </c>
       <c r="D3" t="n">
-        <v>14837</v>
+        <v>15949</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2561</v>
+        <v>1542</v>
       </c>
       <c r="C4" t="n">
-        <v>3972</v>
+        <v>6546</v>
       </c>
       <c r="D4" t="n">
-        <v>8380</v>
+        <v>8038</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1865</v>
+        <v>1021</v>
       </c>
       <c r="C5" t="n">
-        <v>4467</v>
+        <v>5247</v>
       </c>
       <c r="D5" t="n">
-        <v>3603</v>
+        <v>2744</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1206</v>
+        <v>491</v>
       </c>
       <c r="C6" t="n">
-        <v>3468</v>
+        <v>2443</v>
       </c>
       <c r="D6" t="n">
-        <v>1459</v>
+        <v>923</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>634</v>
+        <v>175</v>
       </c>
       <c r="C7" t="n">
-        <v>2041</v>
+        <v>974</v>
       </c>
       <c r="D7" t="n">
-        <v>745</v>
+        <v>526</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>268</v>
+        <v>81</v>
       </c>
       <c r="C8" t="n">
-        <v>1011</v>
+        <v>462</v>
       </c>
       <c r="D8" t="n">
-        <v>460</v>
+        <v>383</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>100</v>
+        <v>57</v>
       </c>
       <c r="C9" t="n">
-        <v>477</v>
+        <v>314</v>
       </c>
       <c r="D9" t="n">
-        <v>324</v>
+        <v>325</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>45</v>
+        <v>31</v>
       </c>
       <c r="C10" t="n">
-        <v>254</v>
+        <v>246</v>
       </c>
       <c r="D10" t="n">
-        <v>249</v>
+        <v>274</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="C11" t="n">
-        <v>182</v>
+        <v>193</v>
       </c>
       <c r="D11" t="n">
-        <v>209</v>
+        <v>216</v>
       </c>
     </row>
     <row r="12">
@@ -1231,13 +1231,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="C12" t="n">
-        <v>144</v>
+        <v>133</v>
       </c>
       <c r="D12" t="n">
-        <v>160</v>
+        <v>176</v>
       </c>
     </row>
     <row r="13">
@@ -1245,13 +1245,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="C13" t="n">
-        <v>108</v>
+        <v>89</v>
       </c>
       <c r="D13" t="n">
-        <v>128</v>
+        <v>142</v>
       </c>
     </row>
     <row r="14">
@@ -1259,13 +1259,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C14" t="n">
-        <v>85</v>
+        <v>71</v>
       </c>
       <c r="D14" t="n">
-        <v>101</v>
+        <v>93</v>
       </c>
     </row>
     <row r="15">
@@ -1276,10 +1276,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D15" t="n">
-        <v>80</v>
+        <v>72</v>
       </c>
     </row>
     <row r="16">
@@ -1290,10 +1290,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>50</v>
+        <v>62</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>52</v>
       </c>
     </row>
     <row r="17">
@@ -1301,13 +1301,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C17" t="n">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>35</v>
       </c>
     </row>
     <row r="18">
@@ -1315,13 +1315,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>35</v>
+        <v>94</v>
       </c>
       <c r="D18" t="n">
-        <v>40</v>
+        <v>18</v>
       </c>
     </row>
     <row r="19">
@@ -1332,10 +1332,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>79</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>3</v>
       </c>
     </row>
     <row r="20">
@@ -1346,10 +1346,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>106</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>9507</v>
+        <v>510</v>
       </c>
       <c r="C2" t="n">
-        <v>7414</v>
+        <v>2136</v>
       </c>
       <c r="D2" t="n">
-        <v>30122</v>
+        <v>16760</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3705</v>
+        <v>1157</v>
       </c>
       <c r="C3" t="n">
-        <v>4396</v>
+        <v>4319</v>
       </c>
       <c r="D3" t="n">
-        <v>15206</v>
+        <v>16657</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2531</v>
+        <v>1667</v>
       </c>
       <c r="C4" t="n">
-        <v>3728</v>
+        <v>6065</v>
       </c>
       <c r="D4" t="n">
-        <v>9036</v>
+        <v>9090</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1914</v>
+        <v>1042</v>
       </c>
       <c r="C5" t="n">
-        <v>4155</v>
+        <v>6255</v>
       </c>
       <c r="D5" t="n">
-        <v>4227</v>
+        <v>3178</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1361</v>
+        <v>382</v>
       </c>
       <c r="C6" t="n">
-        <v>3824</v>
+        <v>3246</v>
       </c>
       <c r="D6" t="n">
-        <v>1734</v>
+        <v>941</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>776</v>
+        <v>76</v>
       </c>
       <c r="C7" t="n">
-        <v>2641</v>
+        <v>991</v>
       </c>
       <c r="D7" t="n">
-        <v>842</v>
+        <v>554</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>365</v>
+        <v>52</v>
       </c>
       <c r="C8" t="n">
-        <v>1414</v>
+        <v>475</v>
       </c>
       <c r="D8" t="n">
-        <v>489</v>
+        <v>434</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>144</v>
+        <v>28</v>
       </c>
       <c r="C9" t="n">
-        <v>681</v>
+        <v>241</v>
       </c>
       <c r="D9" t="n">
-        <v>339</v>
+        <v>370</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>58</v>
+        <v>14</v>
       </c>
       <c r="C10" t="n">
-        <v>339</v>
+        <v>189</v>
       </c>
       <c r="D10" t="n">
-        <v>253</v>
+        <v>211</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>30</v>
+        <v>9</v>
       </c>
       <c r="C11" t="n">
-        <v>206</v>
+        <v>130</v>
       </c>
       <c r="D11" t="n">
-        <v>211</v>
+        <v>172</v>
       </c>
     </row>
     <row r="12">
@@ -1542,13 +1542,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="C12" t="n">
-        <v>157</v>
+        <v>87</v>
       </c>
       <c r="D12" t="n">
-        <v>162</v>
+        <v>139</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="C13" t="n">
-        <v>118</v>
+        <v>69</v>
       </c>
       <c r="D13" t="n">
-        <v>130</v>
+        <v>91</v>
       </c>
     </row>
     <row r="14">
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>91</v>
+        <v>62</v>
       </c>
       <c r="D14" t="n">
-        <v>101</v>
+        <v>70</v>
       </c>
     </row>
     <row r="15">
@@ -1584,13 +1584,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>71</v>
+        <v>60</v>
       </c>
       <c r="D15" t="n">
-        <v>81</v>
+        <v>50</v>
       </c>
     </row>
     <row r="16">
@@ -1598,13 +1598,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C16" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>34</v>
       </c>
     </row>
     <row r="17">
@@ -1612,13 +1612,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="C17" t="n">
-        <v>42</v>
+        <v>92</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>17</v>
       </c>
     </row>
     <row r="18">
@@ -1626,13 +1626,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>35</v>
+        <v>77</v>
       </c>
       <c r="D18" t="n">
-        <v>40</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19">
@@ -1643,10 +1643,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1657,10 +1657,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>112</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8373</v>
+        <v>1268</v>
       </c>
       <c r="C2" t="n">
-        <v>4922</v>
+        <v>4824</v>
       </c>
       <c r="D2" t="n">
-        <v>24440</v>
+        <v>15368</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4555</v>
+        <v>733</v>
       </c>
       <c r="C3" t="n">
-        <v>6695</v>
+        <v>2798</v>
       </c>
       <c r="D3" t="n">
-        <v>16943</v>
+        <v>15500</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1768</v>
+        <v>1281</v>
       </c>
       <c r="C4" t="n">
-        <v>6100</v>
+        <v>5058</v>
       </c>
       <c r="D4" t="n">
-        <v>8866</v>
+        <v>10193</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1257</v>
+        <v>1188</v>
       </c>
       <c r="C5" t="n">
-        <v>3747</v>
+        <v>6088</v>
       </c>
       <c r="D5" t="n">
-        <v>2876</v>
+        <v>4133</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>717</v>
+        <v>596</v>
       </c>
       <c r="C6" t="n">
-        <v>2588</v>
+        <v>4720</v>
       </c>
       <c r="D6" t="n">
-        <v>825</v>
+        <v>1271</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>337</v>
+        <v>164</v>
       </c>
       <c r="C7" t="n">
-        <v>1385</v>
+        <v>2026</v>
       </c>
       <c r="D7" t="n">
-        <v>479</v>
+        <v>610</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>133</v>
+        <v>57</v>
       </c>
       <c r="C8" t="n">
-        <v>667</v>
+        <v>696</v>
       </c>
       <c r="D8" t="n">
-        <v>332</v>
+        <v>449</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>53</v>
+        <v>32</v>
       </c>
       <c r="C9" t="n">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="D9" t="n">
-        <v>247</v>
+        <v>376</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="C10" t="n">
-        <v>201</v>
+        <v>213</v>
       </c>
       <c r="D10" t="n">
-        <v>206</v>
+        <v>227</v>
       </c>
     </row>
     <row r="11">
@@ -1839,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="C11" t="n">
         <v>153</v>
       </c>
       <c r="D11" t="n">
-        <v>158</v>
+        <v>177</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="C12" t="n">
-        <v>115</v>
+        <v>100</v>
       </c>
       <c r="D12" t="n">
-        <v>127</v>
+        <v>145</v>
       </c>
     </row>
     <row r="13">
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C13" t="n">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="D13" t="n">
-        <v>98</v>
+        <v>91</v>
       </c>
     </row>
     <row r="14">
@@ -1881,13 +1881,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C14" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D14" t="n">
-        <v>79</v>
+        <v>70</v>
       </c>
     </row>
     <row r="15">
@@ -1898,10 +1898,10 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>51</v>
+        <v>66</v>
       </c>
       <c r="D15" t="n">
-        <v>63</v>
+        <v>49</v>
       </c>
     </row>
     <row r="16">
@@ -1909,13 +1909,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="C16" t="n">
-        <v>41</v>
+        <v>90</v>
       </c>
       <c r="D16" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
     </row>
     <row r="17">
@@ -1926,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>34</v>
+        <v>102</v>
       </c>
       <c r="D17" t="n">
-        <v>39</v>
+        <v>11</v>
       </c>
     </row>
     <row r="18">
@@ -1940,10 +1940,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>31</v>
+        <v>3</v>
       </c>
       <c r="D18" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1954,10 +1954,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1965,13 +1965,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>112</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4822</v>
+        <v>709</v>
       </c>
       <c r="C2" t="n">
-        <v>2396</v>
+        <v>2939</v>
       </c>
       <c r="D2" t="n">
-        <v>16490</v>
+        <v>12247</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5335</v>
+        <v>815</v>
       </c>
       <c r="C3" t="n">
-        <v>5300</v>
+        <v>3376</v>
       </c>
       <c r="D3" t="n">
-        <v>17182</v>
+        <v>14589</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2472</v>
+        <v>1010</v>
       </c>
       <c r="C4" t="n">
-        <v>6492</v>
+        <v>4035</v>
       </c>
       <c r="D4" t="n">
-        <v>10007</v>
+        <v>10796</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1378</v>
+        <v>1205</v>
       </c>
       <c r="C5" t="n">
-        <v>4842</v>
+        <v>5760</v>
       </c>
       <c r="D5" t="n">
-        <v>3591</v>
+        <v>4901</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>867</v>
+        <v>719</v>
       </c>
       <c r="C6" t="n">
-        <v>3131</v>
+        <v>5412</v>
       </c>
       <c r="D6" t="n">
-        <v>1036</v>
+        <v>1582</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>320</v>
+        <v>191</v>
       </c>
       <c r="C7" t="n">
-        <v>1848</v>
+        <v>2982</v>
       </c>
       <c r="D7" t="n">
-        <v>522</v>
+        <v>683</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>112</v>
+        <v>54</v>
       </c>
       <c r="C8" t="n">
-        <v>884</v>
+        <v>1050</v>
       </c>
       <c r="D8" t="n">
-        <v>346</v>
+        <v>483</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>43</v>
+        <v>27</v>
       </c>
       <c r="C9" t="n">
-        <v>391</v>
+        <v>431</v>
       </c>
       <c r="D9" t="n">
-        <v>259</v>
+        <v>374</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="C10" t="n">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="D10" t="n">
-        <v>211</v>
+        <v>235</v>
       </c>
     </row>
     <row r="11">
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="C11" t="n">
-        <v>169</v>
+        <v>157</v>
       </c>
       <c r="D11" t="n">
-        <v>167</v>
+        <v>185</v>
       </c>
     </row>
     <row r="12">
@@ -2164,13 +2164,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C12" t="n">
-        <v>99</v>
+        <v>109</v>
       </c>
       <c r="D12" t="n">
-        <v>131</v>
+        <v>137</v>
       </c>
     </row>
     <row r="13">
@@ -2178,13 +2178,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D13" t="n">
-        <v>99</v>
+        <v>94</v>
       </c>
     </row>
     <row r="14">
@@ -2195,10 +2195,10 @@
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>49</v>
+        <v>64</v>
       </c>
       <c r="D14" t="n">
-        <v>61</v>
+        <v>54</v>
       </c>
     </row>
     <row r="15">
@@ -2206,13 +2206,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="C15" t="n">
-        <v>40</v>
+        <v>88</v>
       </c>
       <c r="D15" t="n">
-        <v>49</v>
+        <v>29</v>
       </c>
     </row>
     <row r="16">
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>33</v>
+        <v>99</v>
       </c>
       <c r="D16" t="n">
-        <v>38</v>
+        <v>10</v>
       </c>
     </row>
     <row r="17">
@@ -2237,10 +2237,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>30</v>
+        <v>2</v>
       </c>
       <c r="D17" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2262,13 +2262,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>109</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4988</v>
+        <v>596</v>
       </c>
       <c r="C2" t="n">
-        <v>4364</v>
+        <v>3173</v>
       </c>
       <c r="D2" t="n">
-        <v>15021</v>
+        <v>25119</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4288</v>
+        <v>646</v>
       </c>
       <c r="C3" t="n">
-        <v>3426</v>
+        <v>2810</v>
       </c>
       <c r="D3" t="n">
-        <v>15900</v>
+        <v>13388</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3218</v>
+        <v>816</v>
       </c>
       <c r="C4" t="n">
-        <v>5750</v>
+        <v>3628</v>
       </c>
       <c r="D4" t="n">
-        <v>10942</v>
+        <v>11086</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1644</v>
+        <v>1037</v>
       </c>
       <c r="C5" t="n">
-        <v>5595</v>
+        <v>4828</v>
       </c>
       <c r="D5" t="n">
-        <v>4528</v>
+        <v>5610</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>999</v>
+        <v>857</v>
       </c>
       <c r="C6" t="n">
-        <v>3888</v>
+        <v>5569</v>
       </c>
       <c r="D6" t="n">
-        <v>1414</v>
+        <v>2070</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>479</v>
+        <v>342</v>
       </c>
       <c r="C7" t="n">
-        <v>2443</v>
+        <v>4028</v>
       </c>
       <c r="D7" t="n">
-        <v>592</v>
+        <v>808</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>165</v>
+        <v>89</v>
       </c>
       <c r="C8" t="n">
-        <v>1298</v>
+        <v>1855</v>
       </c>
       <c r="D8" t="n">
-        <v>370</v>
+        <v>510</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>58</v>
+        <v>32</v>
       </c>
       <c r="C9" t="n">
-        <v>591</v>
+        <v>671</v>
       </c>
       <c r="D9" t="n">
-        <v>266</v>
+        <v>383</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="C10" t="n">
-        <v>285</v>
+        <v>307</v>
       </c>
       <c r="D10" t="n">
-        <v>216</v>
+        <v>247</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C11" t="n">
-        <v>191</v>
+        <v>183</v>
       </c>
       <c r="D11" t="n">
-        <v>170</v>
+        <v>189</v>
       </c>
     </row>
     <row r="12">
@@ -2475,13 +2475,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C12" t="n">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="D12" t="n">
-        <v>133</v>
+        <v>140</v>
       </c>
     </row>
     <row r="13">
@@ -2492,10 +2492,10 @@
         <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="D13" t="n">
-        <v>100</v>
+        <v>96</v>
       </c>
     </row>
     <row r="14">
@@ -2503,13 +2503,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>54</v>
+        <v>67</v>
       </c>
       <c r="D14" t="n">
-        <v>64</v>
+        <v>56</v>
       </c>
     </row>
     <row r="15">
@@ -2517,13 +2517,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="C15" t="n">
-        <v>44</v>
+        <v>89</v>
       </c>
       <c r="D15" t="n">
-        <v>49</v>
+        <v>28</v>
       </c>
     </row>
     <row r="16">
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>37</v>
+        <v>102</v>
       </c>
       <c r="D16" t="n">
-        <v>37</v>
+        <v>9</v>
       </c>
     </row>
     <row r="17">
@@ -2548,10 +2548,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>32</v>
+        <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2559,13 +2559,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>66</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>59</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2888</v>
+        <v>395</v>
       </c>
       <c r="C2" t="n">
-        <v>1965</v>
+        <v>1624</v>
       </c>
       <c r="D2" t="n">
-        <v>10374</v>
+        <v>18086</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4342</v>
+        <v>853</v>
       </c>
       <c r="C3" t="n">
-        <v>3641</v>
+        <v>3125</v>
       </c>
       <c r="D3" t="n">
-        <v>15419</v>
+        <v>15265</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3578</v>
+        <v>1354</v>
       </c>
       <c r="C4" t="n">
-        <v>5379</v>
+        <v>5173</v>
       </c>
       <c r="D4" t="n">
-        <v>11610</v>
+        <v>11423</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1728</v>
+        <v>868</v>
       </c>
       <c r="C5" t="n">
-        <v>6472</v>
+        <v>7468</v>
       </c>
       <c r="D5" t="n">
-        <v>4905</v>
+        <v>5174</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>867</v>
+        <v>316</v>
       </c>
       <c r="C6" t="n">
-        <v>4775</v>
+        <v>5366</v>
       </c>
       <c r="D6" t="n">
-        <v>1386</v>
+        <v>1727</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>152</v>
+        <v>82</v>
       </c>
       <c r="C7" t="n">
-        <v>2504</v>
+        <v>1817</v>
       </c>
       <c r="D7" t="n">
-        <v>596</v>
+        <v>618</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>53</v>
+        <v>29</v>
       </c>
       <c r="C8" t="n">
-        <v>998</v>
+        <v>657</v>
       </c>
       <c r="D8" t="n">
-        <v>386</v>
+        <v>375</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="C9" t="n">
-        <v>279</v>
+        <v>300</v>
       </c>
       <c r="D9" t="n">
-        <v>292</v>
+        <v>242</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="C10" t="n">
-        <v>187</v>
+        <v>179</v>
       </c>
       <c r="D10" t="n">
-        <v>166</v>
+        <v>185</v>
       </c>
     </row>
     <row r="11">
@@ -2772,13 +2772,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C11" t="n">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="D11" t="n">
-        <v>130</v>
+        <v>137</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="D12" t="n">
-        <v>98</v>
+        <v>94</v>
       </c>
     </row>
     <row r="13">
@@ -2800,13 +2800,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>52</v>
+        <v>65</v>
       </c>
       <c r="D13" t="n">
-        <v>62</v>
+        <v>54</v>
       </c>
     </row>
     <row r="14">
@@ -2814,13 +2814,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="C14" t="n">
-        <v>43</v>
+        <v>87</v>
       </c>
       <c r="D14" t="n">
-        <v>48</v>
+        <v>27</v>
       </c>
     </row>
     <row r="15">
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>36</v>
+        <v>99</v>
       </c>
       <c r="D15" t="n">
-        <v>36</v>
+        <v>8</v>
       </c>
     </row>
     <row r="16">
@@ -2845,10 +2845,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -2856,13 +2856,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>64</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>57</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3877</v>
+        <v>222</v>
       </c>
       <c r="C2" t="n">
-        <v>4470</v>
+        <v>1324</v>
       </c>
       <c r="D2" t="n">
-        <v>13772</v>
+        <v>12596</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3176</v>
+        <v>561</v>
       </c>
       <c r="C3" t="n">
-        <v>2530</v>
+        <v>2087</v>
       </c>
       <c r="D3" t="n">
-        <v>13779</v>
+        <v>14576</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3437</v>
+        <v>933</v>
       </c>
       <c r="C4" t="n">
-        <v>4416</v>
+        <v>3897</v>
       </c>
       <c r="D4" t="n">
-        <v>11878</v>
+        <v>11249</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2197</v>
+        <v>778</v>
       </c>
       <c r="C5" t="n">
-        <v>5885</v>
+        <v>5657</v>
       </c>
       <c r="D5" t="n">
-        <v>5785</v>
+        <v>5429</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1095</v>
+        <v>312</v>
       </c>
       <c r="C6" t="n">
-        <v>5572</v>
+        <v>5164</v>
       </c>
       <c r="D6" t="n">
-        <v>1888</v>
+        <v>1886</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>340</v>
+        <v>72</v>
       </c>
       <c r="C7" t="n">
-        <v>3462</v>
+        <v>2440</v>
       </c>
       <c r="D7" t="n">
-        <v>690</v>
+        <v>614</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>73</v>
+        <v>15</v>
       </c>
       <c r="C8" t="n">
-        <v>1602</v>
+        <v>727</v>
       </c>
       <c r="D8" t="n">
-        <v>410</v>
+        <v>326</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="C9" t="n">
-        <v>523</v>
+        <v>273</v>
       </c>
       <c r="D9" t="n">
-        <v>301</v>
+        <v>194</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="C10" t="n">
-        <v>221</v>
+        <v>132</v>
       </c>
       <c r="D10" t="n">
-        <v>177</v>
+        <v>141</v>
       </c>
     </row>
     <row r="11">
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>139</v>
+        <v>78</v>
       </c>
       <c r="D11" t="n">
-        <v>134</v>
+        <v>100</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>86</v>
+        <v>54</v>
       </c>
       <c r="D12" t="n">
-        <v>100</v>
+        <v>62</v>
       </c>
     </row>
     <row r="13">
@@ -3111,13 +3111,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="D13" t="n">
-        <v>62</v>
+        <v>32</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="D14" t="n">
-        <v>48</v>
+        <v>9</v>
       </c>
     </row>
     <row r="15">
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3153,13 +3153,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>58</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>74</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3184,10 +3184,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2660</v>
+        <v>361</v>
       </c>
       <c r="C2" t="n">
-        <v>2523</v>
+        <v>5520</v>
       </c>
       <c r="D2" t="n">
-        <v>10943</v>
+        <v>11600</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2987</v>
+        <v>335</v>
       </c>
       <c r="C3" t="n">
-        <v>3040</v>
+        <v>1446</v>
       </c>
       <c r="D3" t="n">
-        <v>13138</v>
+        <v>13209</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3091</v>
+        <v>658</v>
       </c>
       <c r="C4" t="n">
-        <v>3612</v>
+        <v>2790</v>
       </c>
       <c r="D4" t="n">
-        <v>11886</v>
+        <v>11545</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2428</v>
+        <v>775</v>
       </c>
       <c r="C5" t="n">
-        <v>5424</v>
+        <v>4630</v>
       </c>
       <c r="D5" t="n">
-        <v>6366</v>
+        <v>6325</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1314</v>
+        <v>482</v>
       </c>
       <c r="C6" t="n">
-        <v>5907</v>
+        <v>5361</v>
       </c>
       <c r="D6" t="n">
-        <v>2294</v>
+        <v>2472</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>332</v>
+        <v>157</v>
       </c>
       <c r="C7" t="n">
-        <v>4256</v>
+        <v>3851</v>
       </c>
       <c r="D7" t="n">
-        <v>781</v>
+        <v>819</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>61</v>
+        <v>33</v>
       </c>
       <c r="C8" t="n">
-        <v>2086</v>
+        <v>1556</v>
       </c>
       <c r="D8" t="n">
-        <v>433</v>
+        <v>367</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="C9" t="n">
-        <v>650</v>
+        <v>480</v>
       </c>
       <c r="D9" t="n">
-        <v>297</v>
+        <v>211</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C10" t="n">
-        <v>230</v>
+        <v>193</v>
       </c>
       <c r="D10" t="n">
-        <v>182</v>
+        <v>148</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>139</v>
+        <v>100</v>
       </c>
       <c r="D11" t="n">
-        <v>136</v>
+        <v>104</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>84</v>
+        <v>63</v>
       </c>
       <c r="D12" t="n">
-        <v>93</v>
+        <v>65</v>
       </c>
     </row>
     <row r="13">
@@ -3422,13 +3422,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="D13" t="n">
-        <v>64</v>
+        <v>34</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>38</v>
+        <v>56</v>
       </c>
       <c r="D14" t="n">
-        <v>38</v>
+        <v>10</v>
       </c>
     </row>
     <row r="15">
@@ -3450,13 +3450,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>56</v>
+        <v>11</v>
       </c>
       <c r="D15" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>72</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3481,10 +3481,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3947</v>
+        <v>341</v>
       </c>
       <c r="C2" t="n">
-        <v>6691</v>
+        <v>7122</v>
       </c>
       <c r="D2" t="n">
-        <v>15461</v>
+        <v>15292</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2407</v>
+        <v>289</v>
       </c>
       <c r="C3" t="n">
-        <v>2495</v>
+        <v>3053</v>
       </c>
       <c r="D3" t="n">
-        <v>11995</v>
+        <v>12161</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2678</v>
+        <v>442</v>
       </c>
       <c r="C4" t="n">
-        <v>3278</v>
+        <v>2022</v>
       </c>
       <c r="D4" t="n">
-        <v>11716</v>
+        <v>11370</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2424</v>
+        <v>662</v>
       </c>
       <c r="C5" t="n">
-        <v>4580</v>
+        <v>3597</v>
       </c>
       <c r="D5" t="n">
-        <v>6967</v>
+        <v>7034</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1590</v>
+        <v>567</v>
       </c>
       <c r="C6" t="n">
-        <v>5660</v>
+        <v>4946</v>
       </c>
       <c r="D6" t="n">
-        <v>2811</v>
+        <v>3067</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>588</v>
+        <v>268</v>
       </c>
       <c r="C7" t="n">
-        <v>4901</v>
+        <v>4574</v>
       </c>
       <c r="D7" t="n">
-        <v>965</v>
+        <v>1061</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>126</v>
+        <v>74</v>
       </c>
       <c r="C8" t="n">
-        <v>2913</v>
+        <v>2612</v>
       </c>
       <c r="D8" t="n">
-        <v>469</v>
+        <v>434</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="C9" t="n">
-        <v>1148</v>
+        <v>954</v>
       </c>
       <c r="D9" t="n">
-        <v>308</v>
+        <v>231</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C10" t="n">
-        <v>363</v>
+        <v>313</v>
       </c>
       <c r="D10" t="n">
-        <v>191</v>
+        <v>153</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>166</v>
+        <v>137</v>
       </c>
       <c r="D11" t="n">
-        <v>140</v>
+        <v>108</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>99</v>
+        <v>77</v>
       </c>
       <c r="D12" t="n">
-        <v>95</v>
+        <v>69</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="D13" t="n">
-        <v>65</v>
+        <v>37</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="D14" t="n">
-        <v>39</v>
+        <v>12</v>
       </c>
     </row>
     <row r="15">
@@ -3761,13 +3761,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>57</v>
+        <v>25</v>
       </c>
       <c r="D15" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>72</v>
+        <v>3</v>
       </c>
       <c r="D16" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5335</v>
+        <v>4402</v>
       </c>
       <c r="C2" t="n">
-        <v>4228</v>
+        <v>7238</v>
       </c>
       <c r="D2" t="n">
-        <v>7494</v>
+        <v>4820</v>
       </c>
     </row>
     <row r="3">
@@ -3904,13 +3904,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>843</v>
+        <v>855</v>
       </c>
     </row>
     <row r="4">
@@ -3918,13 +3918,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>175</v>
+        <v>205</v>
       </c>
       <c r="C4" t="n">
-        <v>313</v>
+        <v>344</v>
       </c>
       <c r="D4" t="n">
-        <v>1805</v>
+        <v>1906</v>
       </c>
     </row>
     <row r="5">
@@ -3932,13 +3932,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>249</v>
+        <v>314</v>
       </c>
       <c r="C5" t="n">
-        <v>515</v>
+        <v>586</v>
       </c>
       <c r="D5" t="n">
-        <v>1038</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="6">
@@ -3946,13 +3946,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>182</v>
+        <v>255</v>
       </c>
       <c r="C6" t="n">
-        <v>395</v>
+        <v>488</v>
       </c>
       <c r="D6" t="n">
-        <v>777</v>
+        <v>898</v>
       </c>
     </row>
     <row r="7">
@@ -3960,13 +3960,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>129</v>
+        <v>202</v>
       </c>
       <c r="C7" t="n">
-        <v>293</v>
+        <v>388</v>
       </c>
       <c r="D7" t="n">
-        <v>496</v>
+        <v>596</v>
       </c>
     </row>
     <row r="8">
@@ -3974,13 +3974,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>99</v>
+        <v>171</v>
       </c>
       <c r="C8" t="n">
-        <v>222</v>
+        <v>307</v>
       </c>
       <c r="D8" t="n">
-        <v>420</v>
+        <v>531</v>
       </c>
     </row>
     <row r="9">
@@ -3988,13 +3988,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>75</v>
+        <v>136</v>
       </c>
       <c r="C9" t="n">
-        <v>187</v>
+        <v>277</v>
       </c>
       <c r="D9" t="n">
-        <v>349</v>
+        <v>445</v>
       </c>
     </row>
     <row r="10">
@@ -4002,13 +4002,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>53</v>
+        <v>105</v>
       </c>
       <c r="C10" t="n">
-        <v>173</v>
+        <v>265</v>
       </c>
       <c r="D10" t="n">
-        <v>362</v>
+        <v>485</v>
       </c>
     </row>
     <row r="11">
@@ -4016,13 +4016,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>34</v>
+        <v>71</v>
       </c>
       <c r="C11" t="n">
-        <v>137</v>
+        <v>215</v>
       </c>
       <c r="D11" t="n">
-        <v>245</v>
+        <v>327</v>
       </c>
     </row>
     <row r="12">
@@ -4030,13 +4030,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="C12" t="n">
-        <v>104</v>
+        <v>169</v>
       </c>
       <c r="D12" t="n">
-        <v>196</v>
+        <v>274</v>
       </c>
     </row>
     <row r="13">
@@ -4044,13 +4044,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="C13" t="n">
-        <v>84</v>
+        <v>142</v>
       </c>
       <c r="D13" t="n">
-        <v>168</v>
+        <v>234</v>
       </c>
     </row>
     <row r="14">
@@ -4058,13 +4058,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="C14" t="n">
-        <v>75</v>
+        <v>128</v>
       </c>
       <c r="D14" t="n">
-        <v>145</v>
+        <v>207</v>
       </c>
     </row>
     <row r="15">
@@ -4072,13 +4072,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="C15" t="n">
-        <v>72</v>
+        <v>127</v>
       </c>
       <c r="D15" t="n">
-        <v>117</v>
+        <v>171</v>
       </c>
     </row>
     <row r="16">
@@ -4086,13 +4086,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>124</v>
       </c>
       <c r="D16" t="n">
-        <v>97</v>
+        <v>140</v>
       </c>
     </row>
     <row r="17">
@@ -4100,13 +4100,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>14</v>
+        <v>36</v>
       </c>
       <c r="C17" t="n">
-        <v>66</v>
+        <v>119</v>
       </c>
       <c r="D17" t="n">
-        <v>76</v>
+        <v>114</v>
       </c>
     </row>
     <row r="18">
@@ -4114,13 +4114,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="C18" t="n">
-        <v>63</v>
+        <v>116</v>
       </c>
       <c r="D18" t="n">
-        <v>57</v>
+        <v>85</v>
       </c>
     </row>
     <row r="19">
@@ -4128,13 +4128,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="C19" t="n">
-        <v>60</v>
+        <v>111</v>
       </c>
       <c r="D19" t="n">
-        <v>38</v>
+        <v>58</v>
       </c>
     </row>
     <row r="20">
@@ -4142,13 +4142,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>109</v>
       </c>
       <c r="D20" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
     </row>
     <row r="21">
@@ -4156,10 +4156,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="C21" t="n">
-        <v>72</v>
+        <v>131</v>
       </c>
       <c r="D21" t="n">
         <v>1</v>
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2763</v>
+        <v>521</v>
       </c>
       <c r="C2" t="n">
-        <v>3693</v>
+        <v>10062</v>
       </c>
       <c r="D2" t="n">
-        <v>11379</v>
+        <v>27074</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3282</v>
+        <v>259</v>
       </c>
       <c r="C3" t="n">
-        <v>3743</v>
+        <v>4314</v>
       </c>
       <c r="D3" t="n">
-        <v>13179</v>
+        <v>11769</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3588</v>
+        <v>326</v>
       </c>
       <c r="C4" t="n">
-        <v>4777</v>
+        <v>2474</v>
       </c>
       <c r="D4" t="n">
-        <v>12177</v>
+        <v>11153</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1581</v>
+        <v>529</v>
       </c>
       <c r="C5" t="n">
-        <v>7404</v>
+        <v>2761</v>
       </c>
       <c r="D5" t="n">
-        <v>6432</v>
+        <v>7418</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>543</v>
+        <v>562</v>
       </c>
       <c r="C6" t="n">
-        <v>6023</v>
+        <v>4288</v>
       </c>
       <c r="D6" t="n">
-        <v>2218</v>
+        <v>3635</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>116</v>
+        <v>354</v>
       </c>
       <c r="C7" t="n">
-        <v>2854</v>
+        <v>4736</v>
       </c>
       <c r="D7" t="n">
-        <v>592</v>
+        <v>1334</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>23</v>
+        <v>131</v>
       </c>
       <c r="C8" t="n">
-        <v>1125</v>
+        <v>3412</v>
       </c>
       <c r="D8" t="n">
-        <v>301</v>
+        <v>521</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5</v>
+        <v>32</v>
       </c>
       <c r="C9" t="n">
-        <v>355</v>
+        <v>1636</v>
       </c>
       <c r="D9" t="n">
-        <v>187</v>
+        <v>256</v>
       </c>
     </row>
     <row r="10">
@@ -4313,13 +4313,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="C10" t="n">
-        <v>162</v>
+        <v>564</v>
       </c>
       <c r="D10" t="n">
-        <v>137</v>
+        <v>159</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>97</v>
+        <v>202</v>
       </c>
       <c r="D11" t="n">
-        <v>93</v>
+        <v>112</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>52</v>
+        <v>97</v>
       </c>
       <c r="D12" t="n">
-        <v>63</v>
+        <v>72</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>39</v>
+        <v>64</v>
       </c>
       <c r="D13" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
     </row>
     <row r="14">
@@ -4369,13 +4369,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
         <v>55</v>
       </c>
       <c r="D14" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
     </row>
     <row r="15">
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>70</v>
+        <v>34</v>
       </c>
       <c r="D15" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -4400,7 +4400,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6700</v>
+        <v>5937</v>
       </c>
       <c r="C2" t="n">
-        <v>6119</v>
+        <v>5000</v>
       </c>
       <c r="D2" t="n">
-        <v>22957</v>
+        <v>21006</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2267</v>
+        <v>1455</v>
       </c>
       <c r="C3" t="n">
-        <v>2164</v>
+        <v>2858</v>
       </c>
       <c r="D3" t="n">
-        <v>1958</v>
+        <v>1283</v>
       </c>
     </row>
     <row r="4">
@@ -4540,13 +4540,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="C4" t="n">
-        <v>114</v>
+        <v>134</v>
       </c>
       <c r="D4" t="n">
-        <v>1538</v>
+        <v>1446</v>
       </c>
     </row>
     <row r="5">
@@ -4554,13 +4554,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>191</v>
+        <v>148</v>
       </c>
       <c r="C5" t="n">
-        <v>384</v>
+        <v>334</v>
       </c>
       <c r="D5" t="n">
-        <v>1161</v>
+        <v>986</v>
       </c>
     </row>
     <row r="6">
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>202</v>
+        <v>143</v>
       </c>
       <c r="C6" t="n">
-        <v>459</v>
+        <v>360</v>
       </c>
       <c r="D6" t="n">
-        <v>808</v>
+        <v>712</v>
       </c>
     </row>
     <row r="7">
@@ -4582,13 +4582,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>145</v>
+        <v>102</v>
       </c>
       <c r="C7" t="n">
-        <v>350</v>
+        <v>277</v>
       </c>
       <c r="D7" t="n">
-        <v>546</v>
+        <v>466</v>
       </c>
     </row>
     <row r="8">
@@ -4596,13 +4596,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>105</v>
+        <v>78</v>
       </c>
       <c r="C8" t="n">
-        <v>260</v>
+        <v>206</v>
       </c>
       <c r="D8" t="n">
-        <v>429</v>
+        <v>384</v>
       </c>
     </row>
     <row r="9">
@@ -4610,13 +4610,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="C9" t="n">
-        <v>205</v>
+        <v>169</v>
       </c>
       <c r="D9" t="n">
-        <v>354</v>
+        <v>313</v>
       </c>
     </row>
     <row r="10">
@@ -4624,13 +4624,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>58</v>
+        <v>44</v>
       </c>
       <c r="C10" t="n">
-        <v>180</v>
+        <v>151</v>
       </c>
       <c r="D10" t="n">
-        <v>356</v>
+        <v>324</v>
       </c>
     </row>
     <row r="11">
@@ -4638,13 +4638,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="C11" t="n">
-        <v>154</v>
+        <v>129</v>
       </c>
       <c r="D11" t="n">
-        <v>261</v>
+        <v>231</v>
       </c>
     </row>
     <row r="12">
@@ -4652,13 +4652,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="C12" t="n">
-        <v>118</v>
+        <v>100</v>
       </c>
       <c r="D12" t="n">
-        <v>199</v>
+        <v>182</v>
       </c>
     </row>
     <row r="13">
@@ -4666,13 +4666,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C13" t="n">
-        <v>93</v>
+        <v>79</v>
       </c>
       <c r="D13" t="n">
-        <v>170</v>
+        <v>154</v>
       </c>
     </row>
     <row r="14">
@@ -4680,13 +4680,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="D14" t="n">
-        <v>146</v>
+        <v>133</v>
       </c>
     </row>
     <row r="15">
@@ -4694,13 +4694,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C15" t="n">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="D15" t="n">
-        <v>118</v>
+        <v>111</v>
       </c>
     </row>
     <row r="16">
@@ -4708,13 +4708,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="D16" t="n">
-        <v>98</v>
+        <v>89</v>
       </c>
     </row>
     <row r="17">
@@ -4722,13 +4722,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C17" t="n">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="D17" t="n">
-        <v>77</v>
+        <v>73</v>
       </c>
     </row>
     <row r="18">
@@ -4736,13 +4736,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C18" t="n">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="D18" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
     </row>
     <row r="19">
@@ -4750,13 +4750,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C19" t="n">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="D19" t="n">
-        <v>39</v>
+        <v>36</v>
       </c>
     </row>
     <row r="20">
@@ -4767,10 +4767,10 @@
         <v>10</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="21">
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C21" t="n">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="D21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4267</v>
+        <v>3468</v>
       </c>
       <c r="C2" t="n">
-        <v>4067</v>
+        <v>4481</v>
       </c>
       <c r="D2" t="n">
-        <v>20925</v>
+        <v>18904</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3680</v>
+        <v>3135</v>
       </c>
       <c r="C3" t="n">
-        <v>3796</v>
+        <v>3560</v>
       </c>
       <c r="D3" t="n">
-        <v>5341</v>
+        <v>4657</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1018</v>
+        <v>698</v>
       </c>
       <c r="C4" t="n">
-        <v>1311</v>
+        <v>1830</v>
       </c>
       <c r="D4" t="n">
-        <v>1575</v>
+        <v>1367</v>
       </c>
     </row>
     <row r="5">
@@ -4865,13 +4865,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>125</v>
+        <v>98</v>
       </c>
       <c r="C5" t="n">
-        <v>220</v>
+        <v>206</v>
       </c>
       <c r="D5" t="n">
-        <v>1186</v>
+        <v>1039</v>
       </c>
     </row>
     <row r="6">
@@ -4879,13 +4879,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>185</v>
+        <v>137</v>
       </c>
       <c r="C6" t="n">
-        <v>411</v>
+        <v>340</v>
       </c>
       <c r="D6" t="n">
-        <v>864</v>
+        <v>756</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>159</v>
+        <v>114</v>
       </c>
       <c r="C7" t="n">
-        <v>409</v>
+        <v>324</v>
       </c>
       <c r="D7" t="n">
-        <v>589</v>
+        <v>509</v>
       </c>
     </row>
     <row r="8">
@@ -4907,13 +4907,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>115</v>
+        <v>83</v>
       </c>
       <c r="C8" t="n">
-        <v>307</v>
+        <v>245</v>
       </c>
       <c r="D8" t="n">
-        <v>441</v>
+        <v>395</v>
       </c>
     </row>
     <row r="9">
@@ -4921,13 +4921,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>84</v>
+        <v>64</v>
       </c>
       <c r="C9" t="n">
-        <v>232</v>
+        <v>190</v>
       </c>
       <c r="D9" t="n">
-        <v>363</v>
+        <v>319</v>
       </c>
     </row>
     <row r="10">
@@ -4935,13 +4935,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>63</v>
+        <v>47</v>
       </c>
       <c r="C10" t="n">
-        <v>190</v>
+        <v>160</v>
       </c>
       <c r="D10" t="n">
-        <v>352</v>
+        <v>318</v>
       </c>
     </row>
     <row r="11">
@@ -4949,13 +4949,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="C11" t="n">
-        <v>166</v>
+        <v>139</v>
       </c>
       <c r="D11" t="n">
-        <v>270</v>
+        <v>244</v>
       </c>
     </row>
     <row r="12">
@@ -4963,13 +4963,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="C12" t="n">
-        <v>134</v>
+        <v>113</v>
       </c>
       <c r="D12" t="n">
-        <v>206</v>
+        <v>186</v>
       </c>
     </row>
     <row r="13">
@@ -4977,13 +4977,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="C13" t="n">
-        <v>103</v>
+        <v>88</v>
       </c>
       <c r="D13" t="n">
-        <v>172</v>
+        <v>156</v>
       </c>
     </row>
     <row r="14">
@@ -4991,13 +4991,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>84</v>
+        <v>73</v>
       </c>
       <c r="D14" t="n">
-        <v>146</v>
+        <v>134</v>
       </c>
     </row>
     <row r="15">
@@ -5005,13 +5005,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C15" t="n">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="D15" t="n">
-        <v>120</v>
+        <v>112</v>
       </c>
     </row>
     <row r="16">
@@ -5019,13 +5019,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="D16" t="n">
-        <v>98</v>
+        <v>90</v>
       </c>
     </row>
     <row r="17">
@@ -5033,13 +5033,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C17" t="n">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="D17" t="n">
-        <v>78</v>
+        <v>74</v>
       </c>
     </row>
     <row r="18">
@@ -5047,13 +5047,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>59</v>
+        <v>55</v>
       </c>
     </row>
     <row r="19">
@@ -5061,13 +5061,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C19" t="n">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="D19" t="n">
-        <v>40</v>
+        <v>37</v>
       </c>
     </row>
     <row r="20">
@@ -5078,10 +5078,10 @@
         <v>9</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="21">
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C21" t="n">
-        <v>106</v>
+        <v>92</v>
       </c>
       <c r="D21" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4767</v>
+        <v>2813</v>
       </c>
       <c r="C2" t="n">
-        <v>6252</v>
+        <v>5288</v>
       </c>
       <c r="D2" t="n">
-        <v>24627</v>
+        <v>27713</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3271</v>
+        <v>2724</v>
       </c>
       <c r="C3" t="n">
-        <v>3413</v>
+        <v>3522</v>
       </c>
       <c r="D3" t="n">
-        <v>7449</v>
+        <v>6707</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1987</v>
+        <v>1680</v>
       </c>
       <c r="C4" t="n">
-        <v>2691</v>
+        <v>2838</v>
       </c>
       <c r="D4" t="n">
-        <v>2250</v>
+        <v>1975</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>478</v>
+        <v>349</v>
       </c>
       <c r="C5" t="n">
-        <v>810</v>
+        <v>1152</v>
       </c>
       <c r="D5" t="n">
-        <v>1209</v>
+        <v>1073</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>147</v>
+        <v>111</v>
       </c>
       <c r="C6" t="n">
-        <v>303</v>
+        <v>259</v>
       </c>
       <c r="D6" t="n">
-        <v>910</v>
+        <v>799</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>160</v>
+        <v>117</v>
       </c>
       <c r="C7" t="n">
-        <v>409</v>
+        <v>332</v>
       </c>
       <c r="D7" t="n">
-        <v>625</v>
+        <v>549</v>
       </c>
     </row>
     <row r="8">
@@ -5218,13 +5218,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>124</v>
+        <v>90</v>
       </c>
       <c r="C8" t="n">
-        <v>358</v>
+        <v>287</v>
       </c>
       <c r="D8" t="n">
-        <v>462</v>
+        <v>407</v>
       </c>
     </row>
     <row r="9">
@@ -5232,13 +5232,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>91</v>
+        <v>68</v>
       </c>
       <c r="C9" t="n">
-        <v>266</v>
+        <v>218</v>
       </c>
       <c r="D9" t="n">
-        <v>372</v>
+        <v>329</v>
       </c>
     </row>
     <row r="10">
@@ -5246,13 +5246,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>66</v>
+        <v>50</v>
       </c>
       <c r="C10" t="n">
-        <v>210</v>
+        <v>174</v>
       </c>
       <c r="D10" t="n">
-        <v>346</v>
+        <v>314</v>
       </c>
     </row>
     <row r="11">
@@ -5260,13 +5260,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>47</v>
+        <v>36</v>
       </c>
       <c r="C11" t="n">
-        <v>176</v>
+        <v>149</v>
       </c>
       <c r="D11" t="n">
-        <v>280</v>
+        <v>250</v>
       </c>
     </row>
     <row r="12">
@@ -5274,13 +5274,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C12" t="n">
-        <v>148</v>
+        <v>124</v>
       </c>
       <c r="D12" t="n">
-        <v>211</v>
+        <v>193</v>
       </c>
     </row>
     <row r="13">
@@ -5288,13 +5288,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="C13" t="n">
-        <v>115</v>
+        <v>98</v>
       </c>
       <c r="D13" t="n">
-        <v>175</v>
+        <v>158</v>
       </c>
     </row>
     <row r="14">
@@ -5302,13 +5302,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="D14" t="n">
-        <v>148</v>
+        <v>134</v>
       </c>
     </row>
     <row r="15">
@@ -5316,13 +5316,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C15" t="n">
-        <v>77</v>
+        <v>68</v>
       </c>
       <c r="D15" t="n">
-        <v>120</v>
+        <v>113</v>
       </c>
     </row>
     <row r="16">
@@ -5330,13 +5330,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C16" t="n">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="D16" t="n">
-        <v>99</v>
+        <v>91</v>
       </c>
     </row>
     <row r="17">
@@ -5344,13 +5344,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C17" t="n">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="D17" t="n">
-        <v>79</v>
+        <v>75</v>
       </c>
     </row>
     <row r="18">
@@ -5358,13 +5358,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>59</v>
+        <v>55</v>
       </c>
     </row>
     <row r="19">
@@ -5372,13 +5372,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C19" t="n">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
     <row r="20">
@@ -5389,10 +5389,10 @@
         <v>8</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="21">
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C21" t="n">
-        <v>122</v>
+        <v>106</v>
       </c>
       <c r="D21" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5725</v>
+        <v>2122</v>
       </c>
       <c r="C2" t="n">
-        <v>9181</v>
+        <v>5294</v>
       </c>
       <c r="D2" t="n">
-        <v>28892</v>
+        <v>31740</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3269</v>
+        <v>2285</v>
       </c>
       <c r="C3" t="n">
-        <v>4292</v>
+        <v>3890</v>
       </c>
       <c r="D3" t="n">
-        <v>9535</v>
+        <v>9585</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2224</v>
+        <v>1904</v>
       </c>
       <c r="C4" t="n">
-        <v>2997</v>
+        <v>3172</v>
       </c>
       <c r="D4" t="n">
-        <v>3108</v>
+        <v>2804</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1026</v>
+        <v>857</v>
       </c>
       <c r="C5" t="n">
-        <v>1786</v>
+        <v>2066</v>
       </c>
       <c r="D5" t="n">
-        <v>1362</v>
+        <v>1213</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>271</v>
+        <v>207</v>
       </c>
       <c r="C6" t="n">
-        <v>557</v>
+        <v>736</v>
       </c>
       <c r="D6" t="n">
-        <v>949</v>
+        <v>837</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>145</v>
+        <v>107</v>
       </c>
       <c r="C7" t="n">
-        <v>351</v>
+        <v>293</v>
       </c>
       <c r="D7" t="n">
-        <v>659</v>
+        <v>582</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>129</v>
+        <v>94</v>
       </c>
       <c r="C8" t="n">
-        <v>382</v>
+        <v>309</v>
       </c>
       <c r="D8" t="n">
-        <v>484</v>
+        <v>427</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>97</v>
+        <v>72</v>
       </c>
       <c r="C9" t="n">
-        <v>309</v>
+        <v>251</v>
       </c>
       <c r="D9" t="n">
-        <v>378</v>
+        <v>338</v>
       </c>
     </row>
     <row r="10">
@@ -5557,13 +5557,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>70</v>
+        <v>53</v>
       </c>
       <c r="C10" t="n">
-        <v>233</v>
+        <v>194</v>
       </c>
       <c r="D10" t="n">
-        <v>346</v>
+        <v>310</v>
       </c>
     </row>
     <row r="11">
@@ -5571,13 +5571,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="C11" t="n">
-        <v>190</v>
+        <v>158</v>
       </c>
       <c r="D11" t="n">
-        <v>286</v>
+        <v>257</v>
       </c>
     </row>
     <row r="12">
@@ -5585,13 +5585,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="C12" t="n">
-        <v>159</v>
+        <v>134</v>
       </c>
       <c r="D12" t="n">
-        <v>216</v>
+        <v>199</v>
       </c>
     </row>
     <row r="13">
@@ -5599,13 +5599,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="C13" t="n">
-        <v>127</v>
+        <v>108</v>
       </c>
       <c r="D13" t="n">
-        <v>178</v>
+        <v>159</v>
       </c>
     </row>
     <row r="14">
@@ -5613,13 +5613,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>100</v>
+        <v>87</v>
       </c>
       <c r="D14" t="n">
-        <v>148</v>
+        <v>135</v>
       </c>
     </row>
     <row r="15">
@@ -5627,13 +5627,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C15" t="n">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="D15" t="n">
-        <v>122</v>
+        <v>114</v>
       </c>
     </row>
     <row r="16">
@@ -5641,13 +5641,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C16" t="n">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="D16" t="n">
-        <v>99</v>
+        <v>91</v>
       </c>
     </row>
     <row r="17">
@@ -5655,13 +5655,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C17" t="n">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="D17" t="n">
-        <v>80</v>
+        <v>76</v>
       </c>
     </row>
     <row r="18">
@@ -5669,13 +5669,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>60</v>
+        <v>56</v>
       </c>
     </row>
     <row r="19">
@@ -5683,13 +5683,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C19" t="n">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
     <row r="20">
@@ -5700,10 +5700,10 @@
         <v>7</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="21">
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C21" t="n">
-        <v>137</v>
+        <v>120</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5892</v>
+        <v>2357</v>
       </c>
       <c r="C2" t="n">
-        <v>8186</v>
+        <v>8811</v>
       </c>
       <c r="D2" t="n">
-        <v>25512</v>
+        <v>30365</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3260</v>
+        <v>1846</v>
       </c>
       <c r="C3" t="n">
-        <v>5598</v>
+        <v>4019</v>
       </c>
       <c r="D3" t="n">
-        <v>11106</v>
+        <v>12277</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1716</v>
+        <v>1790</v>
       </c>
       <c r="C4" t="n">
-        <v>3053</v>
+        <v>3498</v>
       </c>
       <c r="D4" t="n">
-        <v>3627</v>
+        <v>3928</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>848</v>
+        <v>1189</v>
       </c>
       <c r="C5" t="n">
-        <v>1773</v>
+        <v>2606</v>
       </c>
       <c r="D5" t="n">
-        <v>1329</v>
+        <v>1466</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>309</v>
+        <v>457</v>
       </c>
       <c r="C6" t="n">
-        <v>788</v>
+        <v>1404</v>
       </c>
       <c r="D6" t="n">
-        <v>768</v>
+        <v>890</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>91</v>
+        <v>140</v>
       </c>
       <c r="C7" t="n">
-        <v>290</v>
+        <v>511</v>
       </c>
       <c r="D7" t="n">
-        <v>520</v>
+        <v>612</v>
       </c>
     </row>
     <row r="8">
@@ -5840,13 +5840,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>58</v>
+        <v>93</v>
       </c>
       <c r="C8" t="n">
-        <v>222</v>
+        <v>301</v>
       </c>
       <c r="D8" t="n">
-        <v>364</v>
+        <v>448</v>
       </c>
     </row>
     <row r="9">
@@ -5854,13 +5854,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>44</v>
+        <v>75</v>
       </c>
       <c r="C9" t="n">
-        <v>201</v>
+        <v>278</v>
       </c>
       <c r="D9" t="n">
-        <v>270</v>
+        <v>345</v>
       </c>
     </row>
     <row r="10">
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>30</v>
+        <v>56</v>
       </c>
       <c r="C10" t="n">
-        <v>151</v>
+        <v>219</v>
       </c>
       <c r="D10" t="n">
-        <v>237</v>
+        <v>311</v>
       </c>
     </row>
     <row r="11">
@@ -5882,13 +5882,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>21</v>
+        <v>40</v>
       </c>
       <c r="C11" t="n">
-        <v>114</v>
+        <v>173</v>
       </c>
       <c r="D11" t="n">
-        <v>194</v>
+        <v>262</v>
       </c>
     </row>
     <row r="12">
@@ -5896,13 +5896,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="C12" t="n">
-        <v>93</v>
+        <v>143</v>
       </c>
       <c r="D12" t="n">
-        <v>148</v>
+        <v>202</v>
       </c>
     </row>
     <row r="13">
@@ -5910,13 +5910,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="C13" t="n">
-        <v>73</v>
+        <v>117</v>
       </c>
       <c r="D13" t="n">
-        <v>117</v>
+        <v>162</v>
       </c>
     </row>
     <row r="14">
@@ -5924,13 +5924,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>57</v>
+        <v>94</v>
       </c>
       <c r="D14" t="n">
-        <v>97</v>
+        <v>136</v>
       </c>
     </row>
     <row r="15">
@@ -5938,13 +5938,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C15" t="n">
-        <v>45</v>
+        <v>77</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>114</v>
       </c>
     </row>
     <row r="16">
@@ -5952,13 +5952,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="C16" t="n">
-        <v>38</v>
+        <v>67</v>
       </c>
       <c r="D16" t="n">
-        <v>63</v>
+        <v>92</v>
       </c>
     </row>
     <row r="17">
@@ -5966,13 +5966,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C17" t="n">
-        <v>35</v>
+        <v>62</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>76</v>
       </c>
     </row>
     <row r="18">
@@ -5980,13 +5980,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>56</v>
       </c>
     </row>
     <row r="19">
@@ -5994,13 +5994,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>26</v>
+        <v>39</v>
       </c>
     </row>
     <row r="20">
@@ -6008,13 +6008,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>53</v>
       </c>
       <c r="D20" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
     </row>
     <row r="21">
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>75</v>
+        <v>133</v>
       </c>
       <c r="D21" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4548</v>
+        <v>2027</v>
       </c>
       <c r="C2" t="n">
-        <v>4296</v>
+        <v>9562</v>
       </c>
       <c r="D2" t="n">
-        <v>25058</v>
+        <v>34884</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3803</v>
+        <v>1713</v>
       </c>
       <c r="C3" t="n">
-        <v>6125</v>
+        <v>5581</v>
       </c>
       <c r="D3" t="n">
-        <v>12806</v>
+        <v>14037</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2173</v>
+        <v>1577</v>
       </c>
       <c r="C4" t="n">
-        <v>4553</v>
+        <v>3695</v>
       </c>
       <c r="D4" t="n">
-        <v>5096</v>
+        <v>5213</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1152</v>
+        <v>1292</v>
       </c>
       <c r="C5" t="n">
-        <v>2497</v>
+        <v>2997</v>
       </c>
       <c r="D5" t="n">
-        <v>1751</v>
+        <v>1846</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>540</v>
+        <v>714</v>
       </c>
       <c r="C6" t="n">
-        <v>1345</v>
+        <v>1952</v>
       </c>
       <c r="D6" t="n">
-        <v>857</v>
+        <v>971</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>181</v>
+        <v>247</v>
       </c>
       <c r="C7" t="n">
-        <v>572</v>
+        <v>939</v>
       </c>
       <c r="D7" t="n">
-        <v>563</v>
+        <v>643</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>68</v>
+        <v>104</v>
       </c>
       <c r="C8" t="n">
-        <v>257</v>
+        <v>397</v>
       </c>
       <c r="D8" t="n">
-        <v>389</v>
+        <v>469</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>47</v>
+        <v>76</v>
       </c>
       <c r="C9" t="n">
-        <v>212</v>
+        <v>288</v>
       </c>
       <c r="D9" t="n">
-        <v>281</v>
+        <v>353</v>
       </c>
     </row>
     <row r="10">
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>33</v>
+        <v>59</v>
       </c>
       <c r="C10" t="n">
-        <v>176</v>
+        <v>241</v>
       </c>
       <c r="D10" t="n">
-        <v>240</v>
+        <v>312</v>
       </c>
     </row>
     <row r="11">
@@ -6193,13 +6193,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="C11" t="n">
-        <v>132</v>
+        <v>191</v>
       </c>
       <c r="D11" t="n">
-        <v>199</v>
+        <v>266</v>
       </c>
     </row>
     <row r="12">
@@ -6207,13 +6207,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="C12" t="n">
-        <v>103</v>
+        <v>154</v>
       </c>
       <c r="D12" t="n">
-        <v>152</v>
+        <v>205</v>
       </c>
     </row>
     <row r="13">
@@ -6221,13 +6221,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="C13" t="n">
-        <v>82</v>
+        <v>126</v>
       </c>
       <c r="D13" t="n">
-        <v>120</v>
+        <v>165</v>
       </c>
     </row>
     <row r="14">
@@ -6235,13 +6235,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>64</v>
+        <v>101</v>
       </c>
       <c r="D14" t="n">
-        <v>98</v>
+        <v>136</v>
       </c>
     </row>
     <row r="15">
@@ -6249,13 +6249,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C15" t="n">
-        <v>50</v>
+        <v>82</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>115</v>
       </c>
     </row>
     <row r="16">
@@ -6263,13 +6263,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C16" t="n">
-        <v>40</v>
+        <v>70</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>93</v>
       </c>
     </row>
     <row r="17">
@@ -6277,13 +6277,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C17" t="n">
-        <v>36</v>
+        <v>63</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>76</v>
       </c>
     </row>
     <row r="18">
@@ -6291,13 +6291,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>57</v>
       </c>
     </row>
     <row r="19">
@@ -6305,13 +6305,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>39</v>
       </c>
     </row>
     <row r="20">
@@ -6319,13 +6319,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>53</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
     </row>
     <row r="21">
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="C21" t="n">
-        <v>84</v>
+        <v>145</v>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5164</v>
+        <v>1884</v>
       </c>
       <c r="C2" t="n">
-        <v>3640</v>
+        <v>5813</v>
       </c>
       <c r="D2" t="n">
-        <v>24809</v>
+        <v>27204</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3439</v>
+        <v>2540</v>
       </c>
       <c r="C3" t="n">
-        <v>4414</v>
+        <v>8399</v>
       </c>
       <c r="D3" t="n">
-        <v>13844</v>
+        <v>15629</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2582</v>
+        <v>1193</v>
       </c>
       <c r="C4" t="n">
-        <v>5363</v>
+        <v>5218</v>
       </c>
       <c r="D4" t="n">
-        <v>6372</v>
+        <v>4775</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1452</v>
+        <v>659</v>
       </c>
       <c r="C5" t="n">
-        <v>3589</v>
+        <v>1912</v>
       </c>
       <c r="D5" t="n">
-        <v>2340</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>774</v>
+        <v>228</v>
       </c>
       <c r="C6" t="n">
-        <v>1948</v>
+        <v>920</v>
       </c>
       <c r="D6" t="n">
-        <v>1008</v>
+        <v>630</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>318</v>
+        <v>96</v>
       </c>
       <c r="C7" t="n">
-        <v>975</v>
+        <v>389</v>
       </c>
       <c r="D7" t="n">
-        <v>603</v>
+        <v>459</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>110</v>
+        <v>70</v>
       </c>
       <c r="C8" t="n">
-        <v>420</v>
+        <v>282</v>
       </c>
       <c r="D8" t="n">
-        <v>415</v>
+        <v>345</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C9" t="n">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="D9" t="n">
-        <v>293</v>
+        <v>305</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="C10" t="n">
-        <v>193</v>
+        <v>187</v>
       </c>
       <c r="D10" t="n">
-        <v>244</v>
+        <v>260</v>
       </c>
     </row>
     <row r="11">
@@ -6504,13 +6504,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C11" t="n">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D11" t="n">
-        <v>203</v>
+        <v>200</v>
       </c>
     </row>
     <row r="12">
@@ -6518,13 +6518,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C12" t="n">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="D12" t="n">
-        <v>155</v>
+        <v>161</v>
       </c>
     </row>
     <row r="13">
@@ -6535,10 +6535,10 @@
         <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>91</v>
+        <v>98</v>
       </c>
       <c r="D13" t="n">
-        <v>123</v>
+        <v>133</v>
       </c>
     </row>
     <row r="14">
@@ -6546,13 +6546,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C14" t="n">
-        <v>71</v>
+        <v>80</v>
       </c>
       <c r="D14" t="n">
-        <v>100</v>
+        <v>112</v>
       </c>
     </row>
     <row r="15">
@@ -6560,13 +6560,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C15" t="n">
-        <v>55</v>
+        <v>68</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>91</v>
       </c>
     </row>
     <row r="16">
@@ -6574,13 +6574,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C16" t="n">
-        <v>43</v>
+        <v>61</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>74</v>
       </c>
     </row>
     <row r="17">
@@ -6588,13 +6588,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C17" t="n">
-        <v>37</v>
+        <v>57</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
     </row>
     <row r="18">
@@ -6602,13 +6602,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C18" t="n">
-        <v>34</v>
+        <v>54</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="19">
@@ -6616,13 +6616,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>51</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
     </row>
     <row r="20">
@@ -6630,13 +6630,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>145</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
     </row>
     <row r="21">
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>92</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
